--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Desktop\statusaldrin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D087FA9E-DA5C-4FDE-ACC1-FD1CFA4BF269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C7BEE5-0B35-41B2-9708-1E1131FBB2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3105" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -503,7 +503,7 @@
     <t>24/03/2026</t>
   </si>
   <si>
-    <t>Creación de Soluciónnnnnnnnnn</t>
+    <t>Creación de Soluciónnnnnnnnnn2</t>
   </si>
 </sst>
 </file>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Desktop\statusaldrin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C7BEE5-0B35-41B2-9708-1E1131FBB2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78804A9-32F1-4902-AA47-7C117483568A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbMegara" sheetId="1" r:id="rId1"/>
@@ -503,7 +503,7 @@
     <t>24/03/2026</t>
   </si>
   <si>
-    <t>Creación de Soluciónnnnnnnnnn2</t>
+    <t>Creación de Solución</t>
   </si>
 </sst>
 </file>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -402,14 +402,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H11"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="46.1640625" customWidth="1"/>
+    <col min="1" max="1" width="23.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.50390625" customWidth="1"/>
+    <col min="3" max="3" width="14.50390625" customWidth="1"/>
+    <col min="4" max="4" width="14.50390625" customWidth="1"/>
+    <col min="5" max="5" width="50.00390625" customWidth="1"/>
     <col min="6" max="6" width="50.00390625" customWidth="1"/>
-    <col min="7" max="7" width="13.50390625" customWidth="1"/>
-    <col min="8" max="8" width="30.00390625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="35.83203125" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -470,7 +470,7 @@
         <v>NFQ / S3</v>
       </c>
       <c r="E2" t="str">
-        <v>Creación de Solución</v>
+        <v>Creación de Soluciónnn</v>
       </c>
       <c r="F2" t="str" xml:space="preserve">
         <v xml:space="preserve">- Opciones de interfaces compartidas por S3:
@@ -714,14 +714,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H7"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.50390625" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -935,14 +935,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -1054,13 +1054,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H16"/>
   <cols>
-    <col min="1" max="1" width="37.00390625" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="27.33203125" customWidth="1"/>
+    <col min="1" max="1" width="44.00390625" customWidth="1"/>
+    <col min="2" max="2" width="14.50390625" customWidth="1"/>
+    <col min="3" max="3" width="14.50390625" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" customWidth="1"/>
     <col min="5" max="5" width="50.00390625" customWidth="1"/>
     <col min="6" max="6" width="50.00390625" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="17.00390625" customWidth="1"/>
     <col min="8" max="8" width="50.00390625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -400,16 +400,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <cols>
-    <col min="1" max="1" width="23.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.50390625" customWidth="1"/>
-    <col min="3" max="3" width="14.50390625" customWidth="1"/>
-    <col min="4" max="4" width="14.50390625" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" customWidth="1"/>
     <col min="5" max="5" width="50.00390625" customWidth="1"/>
     <col min="6" max="6" width="50.00390625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="35.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="8" width="42.6640625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -456,7 +456,7 @@
         <v>pasos</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
         <v>Sustitución Rundeck.</v>
       </c>
@@ -470,18 +470,16 @@
         <v>NFQ / S3</v>
       </c>
       <c r="E2" t="str">
-        <v>Creación de Soluciónnn</v>
-      </c>
-      <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Opciones de interfaces compartidas por S3:
-CGC Position, Valorized Position,Net Asset, Payable Receivable
-- La POC ha sido presentada.</v>
+        <v>Creación de Solución</v>
+      </c>
+      <c r="F2" t="str">
+        <v>"- Opciones de interfaces compartidas por S3:</v>
       </c>
       <c r="G2" t="str">
         <v>09/04/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>--------</v>
+        <v>-----------------------</v>
       </c>
     </row>
     <row r="3">
@@ -498,13 +496,16 @@
         <v>NFQ / S3</v>
       </c>
       <c r="E3" t="str">
-        <v>function_meg_cart_pos_rv_t</v>
+        <v>function_meg_sac_pl_cl_patrrv_intermedia_t</v>
       </c>
       <c r="F3" t="str">
         <v>- Fue ajustada funcion de mapeamento</v>
       </c>
       <c r="G3" t="str">
-        <v>03/06/2026</v>
+        <v>16/06/2026</v>
+      </c>
+      <c r="H3" t="str">
+        <v>_x000d_</v>
       </c>
     </row>
     <row r="4">
@@ -521,13 +522,16 @@
         <v>NFQ / S3</v>
       </c>
       <c r="E4" t="str">
-        <v>function_meg_sac_pl_cl_patrrv_t</v>
+        <v>function_meg_cart_pos_rf_t</v>
       </c>
       <c r="F4" t="str">
         <v>- Fue ajustada funcion de mapeamento</v>
       </c>
       <c r="G4" t="str">
-        <v>03/06/2026</v>
+        <v>17/06/2026</v>
+      </c>
+      <c r="H4" t="str">
+        <v>_x000d_</v>
       </c>
     </row>
     <row r="5">
@@ -550,7 +554,10 @@
         <v>- Fue ajustada funcion de mapeamento</v>
       </c>
       <c r="G5" t="str">
-        <v>10/06/2026</v>
+        <v>16/06/2026</v>
+      </c>
+      <c r="H5" t="str">
+        <v>_x000d_</v>
       </c>
     </row>
     <row r="6">
@@ -567,13 +574,16 @@
         <v>NFQ / S3</v>
       </c>
       <c r="E6" t="str">
-        <v>function_meg_sac_stat_rv_cadpap_t1</v>
+        <v>function_meg_sac_pl_cl_patrrf_t</v>
       </c>
       <c r="F6" t="str">
         <v>- Fue ajustada funcion de mapeamento</v>
       </c>
       <c r="G6" t="str">
-        <v>29/05/2026</v>
+        <v>16/06/2026</v>
+      </c>
+      <c r="H6" t="str">
+        <v>_x000d_</v>
       </c>
     </row>
     <row r="7">
@@ -590,13 +600,16 @@
         <v>NFQ / S3</v>
       </c>
       <c r="E7" t="str">
-        <v>function_meg_sac_stat_rv_cadpap_t</v>
+        <v>function_meg_sac_pl_cl_patrrv_intermedia_t</v>
       </c>
       <c r="F7" t="str">
         <v>- Fue ajustada funcion de mapeamento</v>
       </c>
       <c r="G7" t="str">
-        <v>09/06/2026</v>
+        <v>17/06/2026</v>
+      </c>
+      <c r="H7" t="str">
+        <v>_x000d_</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +617,7 @@
         <v>Nueva Interfaz</v>
       </c>
       <c r="B8" t="str">
-        <v>En proceso</v>
+        <v>Completado</v>
       </c>
       <c r="C8" t="str">
         <v>PRD</v>
@@ -619,10 +632,10 @@
         <v>- Aguardando Vobo de S3 para implantacion</v>
       </c>
       <c r="G8" t="str">
-        <v>09/06/2026</v>
+        <v>10/06/2026</v>
       </c>
       <c r="H8" t="str">
-        <v>- S3 validará desarrollo</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
     </row>
     <row r="9">
@@ -630,7 +643,7 @@
         <v>Nuevos Campis</v>
       </c>
       <c r="B9" t="str">
-        <v>En proceso</v>
+        <v>Completado</v>
       </c>
       <c r="C9" t="str">
         <v>UAT</v>
@@ -642,13 +655,13 @@
         <v>Client iInstruction</v>
       </c>
       <c r="F9" t="str">
-        <v>- Esperando validación de S3</v>
+        <v>- Esperando validación de S3 para PRD</v>
       </c>
       <c r="G9" t="str">
-        <v>09/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="H9" t="str">
-        <v>- S3 validará desarrollo</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
     </row>
     <row r="10">
@@ -656,10 +669,10 @@
         <v>Nuevos Campis</v>
       </c>
       <c r="B10" t="str">
-        <v>En proceso</v>
+        <v>Completado</v>
       </c>
       <c r="C10" t="str">
-        <v>UAT</v>
+        <v>PRD</v>
       </c>
       <c r="D10" t="str">
         <v>NFQ / S3</v>
@@ -668,13 +681,13 @@
         <v>Valorized Position</v>
       </c>
       <c r="F10" t="str">
-        <v>- Esperado nueva extracción con calidad de informacion por parte de S3</v>
+        <v>- Esperando validación de S3</v>
       </c>
       <c r="G10" t="str">
-        <v>11/06/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="H10" t="str">
-        <v>- S3 compartirá nuevo cml para poder realizar desarrollo</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
     </row>
     <row r="11">
@@ -700,12 +713,38 @@
         <v>27/05/2026</v>
       </c>
       <c r="H11" t="str">
+        <v>- NFQ ajustara segun el orden de prioridad de tareas_x000d_</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Ajuste Option</v>
+      </c>
+      <c r="B12" t="str">
+        <v>En proceso</v>
+      </c>
+      <c r="C12" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D12" t="str">
+        <v>NFQ / S3</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Options</v>
+      </c>
+      <c r="F12" t="str">
+        <v>- Configuración de Rundeck para la interfaz de opciones</v>
+      </c>
+      <c r="G12" t="str">
+        <v>17/06/2026</v>
+      </c>
+      <c r="H12" t="str">
         <v>- NFQ ajustara segun el orden de prioridad de tareas</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -714,14 +753,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H7"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.50390625" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.50390625" customWidth="1"/>
+    <col min="2" max="2" width="24.50390625" customWidth="1"/>
+    <col min="3" max="3" width="24.50390625" customWidth="1"/>
+    <col min="4" max="4" width="24.50390625" customWidth="1"/>
+    <col min="5" max="5" width="24.50390625" customWidth="1"/>
+    <col min="6" max="6" width="24.50390625" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.50390625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -785,13 +824,13 @@
         <v>Creación de reporte: Relatório de Estoque de Cotas de Fundos</v>
       </c>
       <c r="F2" t="str">
-        <v>- Informe Disponibilizado en UAT</v>
+        <v>- Informe Disponibilizado en PRD</v>
       </c>
       <c r="G2" t="str">
         <v>27/05/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>- S3 validará desarrollo</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
     </row>
     <row r="3">
@@ -811,13 +850,13 @@
         <v>Creación de reporte: Relatório de Estoque de Futuros</v>
       </c>
       <c r="F3" t="str">
-        <v>- Informe Disponibilizado en UAT</v>
+        <v>- Informe Disponibilizado en PRD</v>
       </c>
       <c r="G3" t="str">
         <v>27/05/2026</v>
       </c>
       <c r="H3" t="str">
-        <v>- S3 validará desarrollo</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
     </row>
     <row r="4">
@@ -825,7 +864,7 @@
         <v>Nuevos reportes</v>
       </c>
       <c r="B4" t="str">
-        <v>En proceso</v>
+        <v>Completado</v>
       </c>
       <c r="C4" t="str">
         <v>PRD</v>
@@ -837,13 +876,13 @@
         <v>Creación de reporte: Relatório de Estoque de RV</v>
       </c>
       <c r="F4" t="str">
-        <v>- Informe Disponibilizado en UAT</v>
+        <v>- Informe Disponibilizado en PRD</v>
       </c>
       <c r="G4" t="str">
         <v>03/06/2026</v>
       </c>
       <c r="H4" t="str">
-        <v>- S3 validará desarrollo</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
     </row>
     <row r="5">
@@ -863,13 +902,13 @@
         <v>Creación de reporte: Relatório de Estoque de RF</v>
       </c>
       <c r="F5" t="str">
-        <v>- Informe Disponibilizado en UAT</v>
+        <v>- Informe Disponibilizado en PRD</v>
       </c>
       <c r="G5" t="str">
         <v>27/05/2026</v>
       </c>
       <c r="H5" t="str">
-        <v>- S3 validará desarrollo</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
     </row>
     <row r="6">
@@ -895,7 +934,7 @@
         <v>18/05/2026</v>
       </c>
       <c r="H6" t="str">
-        <v>NA</v>
+        <v>NA_x000d_</v>
       </c>
     </row>
     <row r="7">
@@ -935,14 +974,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.50390625" customWidth="1"/>
+    <col min="2" max="2" width="24.50390625" customWidth="1"/>
+    <col min="3" max="3" width="24.50390625" customWidth="1"/>
+    <col min="4" max="4" width="24.50390625" customWidth="1"/>
+    <col min="5" max="5" width="24.50390625" customWidth="1"/>
+    <col min="6" max="6" width="24.50390625" customWidth="1"/>
+    <col min="7" max="7" width="24.50390625" customWidth="1"/>
+    <col min="8" max="8" width="24.50390625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -1009,13 +1048,13 @@
         <v>- Caida de MegaCustody Intraday</v>
       </c>
       <c r="G2" t="str">
-        <v>24/03/2026</v>
+        <v>24/3/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>- Se seguirá compartiendo alerta</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
+        <v>- Se seguirá compartiendo alerta_x000d_</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="str">
         <v>API</v>
       </c>
@@ -1031,10 +1070,8 @@
       <c r="E3" t="str">
         <v>Llamada de MEGARA desde Rundeck</v>
       </c>
-      <c r="F3" t="str" xml:space="preserve">
-        <v xml:space="preserve">- NFQ ha implementado solución y se encuentra operativa en PRD
-- Fallas ocasionaes de lado de Megara (Durante la implementación de las interfaces, Megacustody se bloqueó)
-- La activación manual de Scheduled Megara mientras la API estaba activada ha provocado problemas</v>
+      <c r="F3" t="str">
+        <v>"- NFQ ha implementado solución y se encuentra operativa en PRD</v>
       </c>
       <c r="G3" t="str">
         <v>24/3/2026</v>
@@ -1052,15 +1089,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <cols>
-    <col min="1" max="1" width="44.00390625" customWidth="1"/>
-    <col min="2" max="2" width="14.50390625" customWidth="1"/>
-    <col min="3" max="3" width="14.50390625" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.00390625" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="39.00390625" customWidth="1"/>
     <col min="5" max="5" width="50.00390625" customWidth="1"/>
     <col min="6" max="6" width="50.00390625" customWidth="1"/>
-    <col min="7" max="7" width="17.00390625" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
     <col min="8" max="8" width="50.00390625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
@@ -1108,385 +1145,371 @@
         <v>pasos</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>Detalhado de Estoque de RF</v>
+        <v>Detalhado de Estoque de RF_x000d_</v>
       </c>
       <c r="B2" t="str">
-        <v>En proceso</v>
+        <v>En proceso_x000d_</v>
       </c>
       <c r="C2" t="str">
         <v>PRD</v>
       </c>
       <c r="D2" t="str">
-        <v>S3 / NFQ</v>
+        <v>S3 / NFQ_x000d_</v>
       </c>
       <c r="E2" t="str">
-        <v>Ajuste</v>
-      </c>
-      <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Ajuste de reglas para campos de Lucro / Prejuizo
-- S3 en validación de ajustes hechos por NFQ</v>
+        <v>Ajuste_x000d_</v>
+      </c>
+      <c r="F2" t="str">
+        <v>"- Ajuste de reglas para campos de Lucro / Prejuizo - S3 en validación de ajustes hechos por NFQ"</v>
       </c>
       <c r="G2" t="str">
-        <v>03/04/2026</v>
+        <v>03/04/2026_x000d_</v>
       </c>
       <c r="H2" t="str">
         <v>Aguardando validacion de S3.</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3" t="str">
-        <v>Extrato Simplificado</v>
+        <v>Extrato Simplificado_x000d_</v>
       </c>
       <c r="B3" t="str">
-        <v>En proceso</v>
+        <v>En proceso_x000d_</v>
       </c>
       <c r="C3" t="str">
         <v>PRD</v>
       </c>
       <c r="D3" t="str">
-        <v>S3 / NFQ</v>
+        <v>S3 / NFQ_x000d_</v>
       </c>
       <c r="E3" t="str">
-        <v>Desarrollo</v>
-      </c>
-      <c r="F3" t="str" xml:space="preserve">
-        <v xml:space="preserve">- S3 ha validado PDF y XLSX
-- Liberado en UAT, a la espera de promocion en PRD
-- A la espera que S3 comparta plantilla de CSV</v>
+        <v>Desarrollo_x000d_</v>
+      </c>
+      <c r="F3" t="str">
+        <v>"- S3 ha validado PDF y XLSX - - Liberado en UAT, a la espera de promocion en PRD - - A la espera que S3 comparta plantilla de CSV"</v>
       </c>
       <c r="G3" t="str">
-        <v>29/04/2026</v>
-      </c>
-      <c r="H3" t="str" xml:space="preserve">
-        <v xml:space="preserve">-S3 compartirá template en csv.
--NFQ ya ha vuelto a solicitar a S3 que envíe los archivos</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
+        <v>29/04/2026_x000d_</v>
+      </c>
+      <c r="H3" t="str">
+        <v>"-S3 compartirá template en csv. - -NFQ ya ha vuelto a solicitar a S3 que envíe los archivos"</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="str">
-        <v>Informes Asíncronos</v>
+        <v>Informes Asíncronos_x000d_</v>
       </c>
       <c r="B4" t="str">
-        <v>En proceso</v>
+        <v>En proceso_x000d_</v>
       </c>
       <c r="C4" t="str">
         <v>PRD</v>
       </c>
       <c r="D4" t="str">
-        <v>NTT / NFQ / VERMEG</v>
+        <v>NTT / NFQ / VERMEG_x000d_</v>
       </c>
       <c r="E4" t="str">
-        <v>S3 solicita la creación de informes asíncronos</v>
-      </c>
-      <c r="F4" t="str" xml:space="preserve">
-        <v xml:space="preserve">- NFQ ha compartido calendario de entrega para los informes solicitados.
-- Testes OK de (Fluxo de Caixa, Operacoes Títulos RF)
-- Espernando repuesta de Operacoes com Titulos de Renda Variavel
-- NFQ en desarrollo de 1 informe (Extrato Simplificado)</v>
+        <v>S3 solicita la creación de informes asíncronos_x000d_</v>
+      </c>
+      <c r="F4" t="str">
+        <v>"- NFQ ha compartido calendario de entrega para los informes solicitados. - - Testes OK de (Fluxo de Caixa, Operacoes Títulos RF) - - Espernando repuesta de Operacoes com Titulos de Renda Variavel - - NFQ en desarrollo de 1 informe (Extrato Simplificado)"</v>
       </c>
       <c r="G4" t="str">
-        <v>22/04/2026</v>
-      </c>
-      <c r="H4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Espernado respuesta de Operaciones de Titulos ed Renda Variavel (cliente y fecha)
-S3 entregará informes de Extrato Simplifcado</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
+        <v>22/04/2026_x000d_</v>
+      </c>
+      <c r="H4" t="str">
+        <v>"Espernado respuesta de Operaciones de Titulos ed Renda Variavel (cliente y fecha) - S3 entregará informes de Extrato Simplifcado"</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="str">
-        <v>Nuevas Interfaces</v>
+        <v>Nuevas Interfaces_x000d_</v>
       </c>
       <c r="B5" t="str">
-        <v>En proceso</v>
+        <v>En proceso_x000d_</v>
       </c>
       <c r="C5" t="str">
         <v>PRD</v>
       </c>
       <c r="D5" t="str">
-        <v>NFQ / S3</v>
-      </c>
-      <c r="E5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Creación de 2 nuevas interfaces (Recalculation_Request, 
-Recalculation_Request_Reason)</v>
+        <v>NFQ / S3_x000d_</v>
+      </c>
+      <c r="E5" t="str">
+        <v>"Creación de 2 nuevas interfaces (Recalculation_Request, RecalculationRequest Reason)</v>
       </c>
       <c r="F5" t="str">
         <v>- Desarrollo realizado en UAT.</v>
       </c>
       <c r="G5" t="str">
-        <v>29/04/2026</v>
+        <v>29/04/2026_x000d_</v>
       </c>
       <c r="H5" t="str">
-        <v>- Validación de lado S3 para pomocionar a UAT</v>
+        <v>- Validación de lado S3 para pomocionar a UAT_x000d_</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Mapeo</v>
+        <v>Mapeo_x000d_</v>
       </c>
       <c r="B6" t="str">
-        <v>⚠️</v>
+        <v>⚠️_x000d_</v>
       </c>
       <c r="C6" t="str">
         <v>UAT</v>
       </c>
       <c r="D6" t="str">
-        <v>S3</v>
+        <v>S3_x000d_</v>
       </c>
       <c r="E6" t="str">
-        <v>Validación ajuste en UAT function_meg_sac_stat_cli_addr_t</v>
+        <v>Validación ajuste en UAT function_meg_sac_stat_cli_addr_t_x000d_</v>
       </c>
       <c r="F6" t="str">
         <v>- En espera de validación por parte de S3 para promoción a PRD.</v>
       </c>
       <c r="G6" t="str">
-        <v>07/07/2025</v>
+        <v>07/07/2025_x000d_</v>
       </c>
       <c r="H6" t="str">
-        <v>Validación de lado S3</v>
+        <v>Validación de lado S3_x000d_</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DDBB</v>
+        <v>DDBB_x000d_</v>
       </c>
       <c r="B7" t="str">
-        <v>⚠️</v>
+        <v>⚠️_x000d_</v>
       </c>
       <c r="C7" t="str">
         <v>UAT</v>
       </c>
       <c r="D7" t="str">
-        <v>S3</v>
+        <v>S3_x000d_</v>
       </c>
       <c r="E7" t="str">
-        <v>CA_details_intr</v>
+        <v>CA_details_intr_x000d_</v>
       </c>
       <c r="F7" t="str">
-        <v>- Ajuste de formatos de datos</v>
+        <v>- Ajuste de formatos de datos_x000d_</v>
       </c>
       <c r="G7" t="str">
-        <v>05/09/2025</v>
+        <v>05/09/2025_x000d_</v>
       </c>
       <c r="H7" t="str">
-        <v>Validación de lado S3</v>
+        <v>Validación de lado S3_x000d_</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Creación mapeos</v>
+        <v>Creación mapeos_x000d_</v>
       </c>
       <c r="B8" t="str">
-        <v>⚠️</v>
+        <v>⚠️_x000d_</v>
       </c>
       <c r="C8" t="str">
         <v>UAT</v>
       </c>
       <c r="D8" t="str">
-        <v>NFQ / S3</v>
+        <v>NFQ / S3_x000d_</v>
       </c>
       <c r="E8" t="str">
-        <v>Nuevos Mapeos</v>
+        <v>Nuevos Mapeos_x000d_</v>
       </c>
       <c r="F8" t="str">
-        <v>-Se encuentra en desarrollo 3 nuevos mapeos que utilizaran la extracción InvestCompanyInstitute</v>
+        <v>-Se encuentra en desarrollo 3 nuevos mapeos que utilizaran la extracción InvestCompanyInstitute_x000d_</v>
       </c>
       <c r="G8" t="str">
-        <v>28/10/2025</v>
+        <v>28/10/2025_x000d_</v>
       </c>
       <c r="H8" t="str">
-        <v>Validación de lado S3</v>
+        <v>Validación de lado S3_x000d_</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Ajuste InvestCompanyInstitute</v>
+        <v>Ajuste InvestCompanyInstitute_x000d_</v>
       </c>
       <c r="B9" t="str">
-        <v>⚠️</v>
+        <v>⚠️_x000d_</v>
       </c>
       <c r="C9" t="str">
         <v>UAT</v>
       </c>
       <c r="D9" t="str">
-        <v>NFQ / S3 / Vermeg / NTT</v>
+        <v>NFQ / S3 / Vermeg / NTT_x000d_</v>
       </c>
       <c r="E9" t="str">
-        <v>Subtabla</v>
+        <v>Subtabla_x000d_</v>
       </c>
       <c r="F9" t="str">
         <v>-Se incluyó una nueva subtabla dentro del XSD, se construyó y promocionó a UAT, a espera de validación de S3</v>
       </c>
       <c r="G9" t="str">
-        <v>28/10/2025</v>
+        <v>28/10/2025_x000d_</v>
       </c>
       <c r="H9" t="str">
-        <v>Validación de lado S3</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
+        <v>Validación de lado S3_x000d_</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="str">
-        <v>Mapeo</v>
+        <v>Mapeo_x000d_</v>
       </c>
       <c r="B10" t="str">
-        <v>❗</v>
+        <v>❗_x000d_</v>
       </c>
       <c r="C10" t="str">
         <v>PRD</v>
       </c>
       <c r="D10" t="str">
-        <v>NFQ / S3</v>
+        <v>NFQ / S3_x000d_</v>
       </c>
       <c r="E10" t="str">
-        <v>Errores ejecución de Mapeo</v>
-      </c>
-      <c r="F10" t="str" xml:space="preserve">
-        <v xml:space="preserve">- mt_caixa_tipos (longitud de campo)
-value too long for type character varying(50)
-- Ajuste en UAT conforme acordado, en espera de confirmación por parte de S3 para promoción a producción.</v>
+        <v>Errores ejecución de Mapeo_x000d_</v>
+      </c>
+      <c r="F10" t="str">
+        <v>"- mt_caixa_tipos (longitud de campo) - value too long for type character varying(50) - - Ajuste en UAT conforme acordado, en espera de confirmación por parte de S3 para promoción a producción."</v>
       </c>
       <c r="G10" t="str">
-        <v>31/10/2025</v>
+        <v>31/10/2025_x000d_</v>
       </c>
       <c r="H10" t="str">
-        <v>Validación de lado S3</v>
+        <v>Validación de lado S3_x000d_</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ajuste Proceso de Carga</v>
+        <v>Ajuste Proceso de Carga_x000d_</v>
       </c>
       <c r="B11" t="str">
-        <v>⚠️</v>
+        <v>⚠️_x000d_</v>
       </c>
       <c r="C11" t="str">
         <v>UAT</v>
       </c>
       <c r="D11" t="str">
-        <v>NFQ / S3</v>
+        <v>NFQ / S3_x000d_</v>
       </c>
       <c r="E11" t="str">
-        <v>Ajuste de Interfaz Equity</v>
+        <v>Ajuste de Interfaz Equity_x000d_</v>
       </c>
       <c r="F11" t="str">
-        <v>- Fue incluido un nuevo campo, a espera de validación y promoción a PRD</v>
+        <v>- Fue incluido un nuevo campo, a espera de validación y promoción a PRD_x000d_</v>
       </c>
       <c r="G11" t="str">
-        <v>21/01/2026</v>
+        <v>21/01/2026_x000d_</v>
       </c>
       <c r="H11" t="str">
-        <v>Validación de lado S3</v>
+        <v>Validación de lado S3_x000d_</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ajuste Proceso de Carga</v>
+        <v>Ajuste Proceso de Carga_x000d_</v>
       </c>
       <c r="B12" t="str">
-        <v>⚠️</v>
+        <v>⚠️_x000d_</v>
       </c>
       <c r="C12" t="str">
         <v>UAT</v>
       </c>
       <c r="D12" t="str">
-        <v>NFQ / S3</v>
+        <v>NFQ / S3_x000d_</v>
       </c>
       <c r="E12" t="str">
-        <v>Ajuste de Carga ScriptByClient</v>
+        <v>Ajuste de Carga ScriptByClient_x000d_</v>
       </c>
       <c r="F12" t="str">
-        <v>- Fue realizado un ajuste en la carga de las tablas Megara que alimentan el mapeo SAC_BA_SCRIPT</v>
+        <v>- Fue realizado un ajuste en la carga de las tablas Megara que alimentan el mapeo SAC_BA_SCRIPT_x000d_</v>
       </c>
       <c r="G12" t="str">
-        <v>28/01/2026</v>
+        <v>28/01/2026_x000d_</v>
       </c>
       <c r="H12" t="str">
-        <v>Validación de lado S3</v>
+        <v>Validación de lado S3_x000d_</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Información UAT</v>
+        <v>Información UAT_x000d_</v>
       </c>
       <c r="B13" t="str">
-        <v>⚫</v>
+        <v>⚫_x000d_</v>
       </c>
       <c r="C13" t="str">
         <v>UAT</v>
       </c>
       <c r="D13" t="str">
-        <v>NFQ / S3</v>
+        <v>NFQ / S3_x000d_</v>
       </c>
       <c r="E13" t="str">
-        <v>Monitoreamento de cargas</v>
+        <v>Monitoreamento de cargas_x000d_</v>
       </c>
       <c r="F13" t="str">
-        <v>- Se requerirá de validaciones de información por causa de los mapeos en UAT</v>
+        <v>- Se requerirá de validaciones de información por causa de los mapeos en UAT_x000d_</v>
       </c>
       <c r="G13" t="str">
-        <v>31/10/2025</v>
+        <v>31/10/2025_x000d_</v>
       </c>
       <c r="H13" t="str">
-        <v>- S3 junto con NFQ revisará ambiente, a la espera de activación al equipo de proyecto</v>
+        <v>- S3 junto con NFQ revisará ambiente, a la espera de activación al equipo de proyecto_x000d_</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Datahub Api</v>
+        <v>Datahub Api_x000d_</v>
       </c>
       <c r="B14" t="str">
-        <v>▶️</v>
+        <v>▶️_x000d_</v>
       </c>
       <c r="C14" t="str">
         <v>UAT</v>
       </c>
       <c r="D14" t="str">
-        <v>NFQ / S3</v>
+        <v>NFQ / S3_x000d_</v>
       </c>
       <c r="E14" t="str">
-        <v>dh-motivobloqueio</v>
+        <v>dh-motivobloqueio_x000d_</v>
       </c>
       <c r="F14" t="str">
         <v>- Api Motivo de Bloqueos han sido realizados los ajustes y está pendiente validación por parte de S3</v>
       </c>
       <c r="G14" t="str">
-        <v>21/01/2026</v>
+        <v>21/01/2026_x000d_</v>
       </c>
       <c r="H14" t="str">
         <v>- S3 notificará resultados de validaciones</v>
       </c>
     </row>
-    <row r="15" xml:space="preserve">
+    <row r="15">
       <c r="A15" t="str">
-        <v>Generacion informes</v>
+        <v>Generacion informes_x000d_</v>
       </c>
       <c r="B15" t="str">
-        <v>▶️</v>
+        <v>▶️_x000d_</v>
       </c>
       <c r="C15" t="str">
         <v>PRD</v>
       </c>
       <c r="D15" t="str">
-        <v>S3 / NFQ</v>
+        <v>S3 / NFQ_x000d_</v>
       </c>
       <c r="E15" t="str">
-        <v>Revisión de informes vacos</v>
-      </c>
-      <c r="F15" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Movimentaçao Swap, Dividendos juros apropiados,Posiçao Swap.siendo generados en blanco.
-- Primeros dos arreglados, esperando detalles del tercero.
-</v>
+        <v>Revisión de informes vacos_x000d_</v>
+      </c>
+      <c r="F15" t="str">
+        <v>"- Movimentaçao Swap, Dividendos juros apropiados,Posiçao Swap.siendo generados en blanco. - - Primeros dos arreglados, esperando detalles del tercero.</v>
       </c>
       <c r="G15" t="str">
-        <v>29/01/2026</v>
-      </c>
-      <c r="H15" t="str" xml:space="preserve">
-        <v xml:space="preserve">- S3 validará arreglos en los informes.
-- S3 compartirá detalles de PS para poder dar soporte.</v>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
+        <v>29/01/2026_x000d_</v>
+      </c>
+      <c r="H15" t="str">
+        <v>"- S3 validará arreglos en los informes. - - S3 compartirá detalles de PS para poder dar soporte."</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="str">
         <v>Nota de Liquidaçao de Renda Fixa</v>
       </c>
@@ -1502,10 +1525,8 @@
       <c r="E16" t="str">
         <v>Generación de informe</v>
       </c>
-      <c r="F16" t="str" xml:space="preserve">
-        <v xml:space="preserve">- S3 en análisis de cambio de plantilla para casos sin información.
-- S3 reporta error en generación de informe.
-- NFQ hizo ajustes.</v>
+      <c r="F16" t="str">
+        <v>"- S3 en análisis de cambio de plantilla para casos sin información. - - S3 reporta error en generación de informe. - - NFQ hizo ajustes."</v>
       </c>
       <c r="G16" t="str">
         <v>09/02/2026</v>
@@ -1514,9 +1535,14 @@
         <v>- S3 analizará cambio de plantilla</v>
       </c>
     </row>
+    <row r="17">
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -473,13 +473,13 @@
         <v>Creación de Solución</v>
       </c>
       <c r="F2" t="str">
-        <v>"- Opciones de interfaces compartidas por S3:</v>
+        <v>- Opciones de interfaces compartidas por S3: CGC Position, Valorized Position, Net Asset, Payable Receivable - La POC ha sido presentada.</v>
       </c>
       <c r="G2" t="str">
         <v>09/04/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>-----------------------</v>
+        <v>-----------------------_x000d_</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
         <v>27/05/2026</v>
       </c>
       <c r="H11" t="str">
-        <v>- NFQ ajustara segun el orden de prioridad de tareas_x000d_</v>
+        <v>- NFQ ajustara segun el orden de prioridad de tarefas_x000d_</v>
       </c>
     </row>
     <row r="12">
@@ -739,7 +739,7 @@
         <v>17/06/2026</v>
       </c>
       <c r="H12" t="str">
-        <v>- NFQ ajustara segun el orden de prioridad de tareas</v>
+        <v>- NFQ ajustara segun el orden de prioridad de tarefas</v>
       </c>
     </row>
   </sheetData>
@@ -809,25 +809,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Nuevos reportes</v>
+        <v>Completado</v>
       </c>
       <c r="B2" t="str">
-        <v>Completado</v>
+        <v>PRD</v>
       </c>
       <c r="C2" t="str">
-        <v>PRD</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="D2" t="str">
-        <v>NFQ / S3</v>
+        <v>Creación de reporte: Relatório de Estoque de Cotas de Fundos</v>
       </c>
       <c r="E2" t="str">
-        <v>Creación de reporte: Relatório de Estoque de Cotas de Fundos</v>
+        <v>- Informe Disponibilizado en PRD</v>
       </c>
       <c r="F2" t="str">
-        <v>- Informe Disponibilizado en PRD</v>
+        <v>27/05/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>27/05/2026</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
       <c r="H2" t="str">
         <v>- S3 validará desarrollo_x000d_</v>
@@ -835,25 +835,25 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nuevos reportes</v>
+        <v>Completado</v>
       </c>
       <c r="B3" t="str">
-        <v>Completado</v>
+        <v>PRD</v>
       </c>
       <c r="C3" t="str">
-        <v>PRD</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="D3" t="str">
-        <v>NFQ / S3</v>
+        <v>Creación de reporte: Relatório de Estoque de Futuros</v>
       </c>
       <c r="E3" t="str">
-        <v>Creación de reporte: Relatório de Estoque de Futuros</v>
+        <v>- Informe Disponibilizado en PRD</v>
       </c>
       <c r="F3" t="str">
-        <v>- Informe Disponibilizado en PRD</v>
+        <v>27/05/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>27/05/2026</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
       <c r="H3" t="str">
         <v>- S3 validará desarrollo_x000d_</v>
@@ -861,25 +861,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nuevos reportes</v>
+        <v>Completado</v>
       </c>
       <c r="B4" t="str">
-        <v>Completado</v>
+        <v>PRD</v>
       </c>
       <c r="C4" t="str">
-        <v>PRD</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="D4" t="str">
-        <v>NFQ / S3</v>
+        <v>Creación de reporte: Relatório de Estoque de RV</v>
       </c>
       <c r="E4" t="str">
-        <v>Creación de reporte: Relatório de Estoque de RV</v>
+        <v>- Informe Disponibilizado en PRD</v>
       </c>
       <c r="F4" t="str">
-        <v>- Informe Disponibilizado en PRD</v>
+        <v>03/06/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>03/06/2026</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
       <c r="H4" t="str">
         <v>- S3 validará desarrollo_x000d_</v>
@@ -887,25 +887,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Nuevos reportes</v>
+        <v>Completado</v>
       </c>
       <c r="B5" t="str">
-        <v>Completado</v>
+        <v>PRD</v>
       </c>
       <c r="C5" t="str">
-        <v>PRD</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="D5" t="str">
-        <v>NFQ / S3</v>
+        <v>Creación de reporte: Relatório de Estoque de RF</v>
       </c>
       <c r="E5" t="str">
-        <v>Creación de reporte: Relatório de Estoque de RF</v>
+        <v>- Informe Disponibilizado en PRD</v>
       </c>
       <c r="F5" t="str">
-        <v>- Informe Disponibilizado en PRD</v>
+        <v>27/05/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>27/05/2026</v>
+        <v>- S3 validará desarrollo_x000d_</v>
       </c>
       <c r="H5" t="str">
         <v>- S3 validará desarrollo_x000d_</v>
@@ -913,25 +913,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Demonstrativo de caixa</v>
+        <v>Completado</v>
       </c>
       <c r="B6" t="str">
-        <v>Completado</v>
+        <v>PRD</v>
       </c>
       <c r="C6" t="str">
-        <v>PRD</v>
+        <v>S3 / NFQ / VERMEG</v>
       </c>
       <c r="D6" t="str">
-        <v>S3 / NFQ / VERMEG</v>
+        <v>Saldos</v>
       </c>
       <c r="E6" t="str">
-        <v>Saldos</v>
+        <v>- Vermeg ha modificado la configuración de SupervisionDashboard en PRD para que se ejecute a las 06:00 (Horário de Brasilia)</v>
       </c>
       <c r="F6" t="str">
-        <v>- Vermeg ha modificado la configuración de SupervisionDashboard en PRD para que se ejecute a las 06:00 (Horário de Brasilia)</v>
+        <v>18/05/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>18/05/2026</v>
+        <v>NA_x000d_</v>
       </c>
       <c r="H6" t="str">
         <v>NA_x000d_</v>
@@ -939,25 +939,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Operações com Título de Renda Fixa</v>
+        <v>En proceso</v>
       </c>
       <c r="B7" t="str">
-        <v>En proceso</v>
+        <v>PRD</v>
       </c>
       <c r="C7" t="str">
-        <v>PRD</v>
+        <v>S3 / NFQ / VERMEG</v>
       </c>
       <c r="D7" t="str">
-        <v>S3 / NFQ / VERMEG</v>
+        <v>Reglas</v>
       </c>
       <c r="E7" t="str">
-        <v>Reglas</v>
+        <v>- Se ha ajustado la regla de visualización de los saldos de los fondos MEGARA.</v>
       </c>
       <c r="F7" t="str">
-        <v>- Se ha ajustado la regla de visualización de los saldos de los fondos MEGARA.</v>
+        <v>10/06/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>10/06/2026</v>
+        <v>- Se realizará desarrollo segun orden de priorización</v>
       </c>
       <c r="H7" t="str">
         <v>- Se realizará desarrollo segun orden de priorización</v>
@@ -1071,7 +1071,7 @@
         <v>Llamada de MEGARA desde Rundeck</v>
       </c>
       <c r="F3" t="str">
-        <v>"- NFQ ha implementado solución y se encuentra operativa en PRD</v>
+        <v>- NFQ ha implementado solución y se encuentra operativa en PRD - Fallas ocasionaes de lado de Megara (Durante la implementación de las interfaces, Megacustody se bloqueó) - La activación manual de Scheduled Megara mientras la API estaba activada ha provocado problemas</v>
       </c>
       <c r="G3" t="str">
         <v>24/3/2026</v>
@@ -1089,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <cols>
     <col min="1" max="1" width="50.00390625" customWidth="1"/>
     <col min="2" max="2" width="17.83203125" customWidth="1"/>
@@ -1147,129 +1147,129 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Detalhado de Estoque de RF_x000d_</v>
+        <v>Detalhado de Estoque de RF</v>
       </c>
       <c r="B2" t="str">
-        <v>En proceso_x000d_</v>
+        <v>En proceso</v>
       </c>
       <c r="C2" t="str">
         <v>PRD</v>
       </c>
       <c r="D2" t="str">
-        <v>S3 / NFQ_x000d_</v>
+        <v>S3 / NFQ</v>
       </c>
       <c r="E2" t="str">
-        <v>Ajuste_x000d_</v>
+        <v>Ajuste</v>
       </c>
       <c r="F2" t="str">
-        <v>"- Ajuste de reglas para campos de Lucro / Prejuizo - S3 en validación de ajustes hechos por NFQ"</v>
+        <v>- Ajuste de reglas para campos de Lucro / Prejuizo - S3 en validación de ajustes hechos por NFQ</v>
       </c>
       <c r="G2" t="str">
-        <v>03/04/2026_x000d_</v>
+        <v>03/04/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>Aguardando validacion de S3.</v>
+        <v>Aguardando validacion de S3._x000d_</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Extrato Simplificado_x000d_</v>
+        <v>Extrato Simplificado</v>
       </c>
       <c r="B3" t="str">
-        <v>En proceso_x000d_</v>
+        <v>En proceso</v>
       </c>
       <c r="C3" t="str">
         <v>PRD</v>
       </c>
       <c r="D3" t="str">
-        <v>S3 / NFQ_x000d_</v>
+        <v>S3 / NFQ</v>
       </c>
       <c r="E3" t="str">
-        <v>Desarrollo_x000d_</v>
+        <v>Desarrollo</v>
       </c>
       <c r="F3" t="str">
-        <v>"- S3 ha validado PDF y XLSX - - Liberado en UAT, a la espera de promocion en PRD - - A la espera que S3 comparta plantilla de CSV"</v>
+        <v>- S3 ha validado PDF y XLSX - Liberado en UAT, a la espera de promocion en PRD - A la espera que S3 comparta plantilla de CSV</v>
       </c>
       <c r="G3" t="str">
-        <v>29/04/2026_x000d_</v>
+        <v>29/04/2026</v>
       </c>
       <c r="H3" t="str">
-        <v>"-S3 compartirá template en csv. - -NFQ ya ha vuelto a solicitar a S3 que envíe los archivos"</v>
+        <v>-S3 compartirá template en csv. -NFQ ya ha vuelto a solicitar a S3 que envíe los arquivos_x000d_</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Informes Asíncronos_x000d_</v>
+        <v>Informes Asíncronos</v>
       </c>
       <c r="B4" t="str">
-        <v>En proceso_x000d_</v>
+        <v>En proceso</v>
       </c>
       <c r="C4" t="str">
         <v>PRD</v>
       </c>
       <c r="D4" t="str">
-        <v>NTT / NFQ / VERMEG_x000d_</v>
+        <v>NTT / NFQ / VERMEG</v>
       </c>
       <c r="E4" t="str">
-        <v>S3 solicita la creación de informes asíncronos_x000d_</v>
+        <v>S3 solicita la creación de informes asíncronos</v>
       </c>
       <c r="F4" t="str">
-        <v>"- NFQ ha compartido calendario de entrega para los informes solicitados. - - Testes OK de (Fluxo de Caixa, Operacoes Títulos RF) - - Espernando repuesta de Operacoes com Titulos de Renda Variavel - - NFQ en desarrollo de 1 informe (Extrato Simplificado)"</v>
+        <v>- NFQ ha compartido calendario de entrega para los informes solicitados. - Testes OK de (Fluxo de Caixa, Operacoes Títulos RF) - Espernando repuesta de Operacoes com Titulos de Renda Variavel - NFQ en desarrollo de 1 informe (Extrato Simplificado)</v>
       </c>
       <c r="G4" t="str">
-        <v>22/04/2026_x000d_</v>
+        <v>22/04/2026</v>
       </c>
       <c r="H4" t="str">
-        <v>"Espernado respuesta de Operaciones de Titulos ed Renda Variavel (cliente y fecha) - S3 entregará informes de Extrato Simplifcado"</v>
+        <v>Espernado respuesta de Operaciones de Titulos ed Renda Variavel (cliente y fecha) S3 entregará informes de Extrato Simplifcado_x000d_</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Nuevas Interfaces_x000d_</v>
+        <v>Nuevas Interfaces</v>
       </c>
       <c r="B5" t="str">
-        <v>En proceso_x000d_</v>
+        <v>En proceso</v>
       </c>
       <c r="C5" t="str">
         <v>PRD</v>
       </c>
       <c r="D5" t="str">
-        <v>NFQ / S3_x000d_</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="E5" t="str">
-        <v>"Creación de 2 nuevas interfaces (Recalculation_Request, RecalculationRequest Reason)</v>
+        <v>Creación de 2 nuevas interfaces (Recalculation_Request, Recalculation_Request_Reason)</v>
       </c>
       <c r="F5" t="str">
         <v>- Desarrollo realizado en UAT.</v>
       </c>
       <c r="G5" t="str">
-        <v>29/04/2026_x000d_</v>
+        <v>29/04/2026</v>
       </c>
       <c r="H5" t="str">
-        <v>- Validación de lado S3 para pomocionar a UAT_x000d_</v>
+        <v>- Validación de lado S3 para promocionar a UAT_x000d_</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Mapeo_x000d_</v>
+        <v>Mapeo</v>
       </c>
       <c r="B6" t="str">
-        <v>⚠️_x000d_</v>
+        <v>⚠️UAT</v>
       </c>
       <c r="C6" t="str">
-        <v>UAT</v>
+        <v>S3</v>
       </c>
       <c r="D6" t="str">
-        <v>S3_x000d_</v>
+        <v>Validación ajuste en UAT function_meg_sac_stat_cli_addr_t</v>
       </c>
       <c r="E6" t="str">
-        <v>Validación ajuste en UAT function_meg_sac_stat_cli_addr_t_x000d_</v>
+        <v>- En espera de validación por parte de S3 para promoción a PRD.</v>
       </c>
       <c r="F6" t="str">
         <v>- En espera de validación por parte de S3 para promoción a PRD.</v>
       </c>
       <c r="G6" t="str">
-        <v>07/07/2025_x000d_</v>
+        <v>07/07/2025</v>
       </c>
       <c r="H6" t="str">
         <v>Validación de lado S3_x000d_</v>
@@ -1277,25 +1277,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DDBB_x000d_</v>
+        <v>DDBB</v>
       </c>
       <c r="B7" t="str">
-        <v>⚠️_x000d_</v>
+        <v>⚠️UAT</v>
       </c>
       <c r="C7" t="str">
-        <v>UAT</v>
+        <v>S3</v>
       </c>
       <c r="D7" t="str">
-        <v>S3_x000d_</v>
+        <v>CA_details_intr</v>
       </c>
       <c r="E7" t="str">
-        <v>CA_details_intr_x000d_</v>
+        <v>- Ajuste de formatos de datos</v>
       </c>
       <c r="F7" t="str">
         <v>- Ajuste de formatos de datos_x000d_</v>
       </c>
       <c r="G7" t="str">
-        <v>05/09/2025_x000d_</v>
+        <v>05/09/2025</v>
       </c>
       <c r="H7" t="str">
         <v>Validación de lado S3_x000d_</v>
@@ -1303,25 +1303,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Creación mapeos_x000d_</v>
+        <v>Creación mapeos</v>
       </c>
       <c r="B8" t="str">
-        <v>⚠️_x000d_</v>
+        <v>⚠️UAT</v>
       </c>
       <c r="C8" t="str">
-        <v>UAT</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="D8" t="str">
-        <v>NFQ / S3_x000d_</v>
+        <v>Nuevos Mapeos</v>
       </c>
       <c r="E8" t="str">
-        <v>Nuevos Mapeos_x000d_</v>
+        <v>-Se encuentra en development 3 novos mapeos que utilizaran la extracción InvestCompanyInstitute</v>
       </c>
       <c r="F8" t="str">
         <v>-Se encuentra en desarrollo 3 nuevos mapeos que utilizaran la extracción InvestCompanyInstitute_x000d_</v>
       </c>
       <c r="G8" t="str">
-        <v>28/10/2025_x000d_</v>
+        <v>28/10/2025</v>
       </c>
       <c r="H8" t="str">
         <v>Validación de lado S3_x000d_</v>
@@ -1329,25 +1329,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Ajuste InvestCompanyInstitute_x000d_</v>
+        <v>Ajuste InvestCompanyInstitute</v>
       </c>
       <c r="B9" t="str">
-        <v>⚠️_x000d_</v>
+        <v>⚠️UAT</v>
       </c>
       <c r="C9" t="str">
-        <v>UAT</v>
+        <v>NFQ / S3 / Vermeg / NTT</v>
       </c>
       <c r="D9" t="str">
-        <v>NFQ / S3 / Vermeg / NTT_x000d_</v>
+        <v>Subtabla</v>
       </c>
       <c r="E9" t="str">
-        <v>Subtabla_x000d_</v>
+        <v>-Se incluyó una nueva subtabla dentro del XSD, se construyó y promocionó a UAT, a espera de validación de S3</v>
       </c>
       <c r="F9" t="str">
         <v>-Se incluyó una nueva subtabla dentro del XSD, se construyó y promocionó a UAT, a espera de validación de S3</v>
       </c>
       <c r="G9" t="str">
-        <v>28/10/2025_x000d_</v>
+        <v>28/10/2025</v>
       </c>
       <c r="H9" t="str">
         <v>Validación de lado S3_x000d_</v>
@@ -1355,25 +1355,25 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Mapeo_x000d_</v>
+        <v>Mapeo</v>
       </c>
       <c r="B10" t="str">
-        <v>❗_x000d_</v>
+        <v>❗PRD</v>
       </c>
       <c r="C10" t="str">
-        <v>PRD</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="D10" t="str">
-        <v>NFQ / S3_x000d_</v>
+        <v>Errores ejecución de Mapeo</v>
       </c>
       <c r="E10" t="str">
-        <v>Errores ejecución de Mapeo_x000d_</v>
+        <v>- mt_caixa_tipos (longitud de campo) value too long for type character varying(50) - Ajuste en UAT conforme acordado, en espera de confirmación por parte de S3 para promoción a producción.</v>
       </c>
       <c r="F10" t="str">
-        <v>"- mt_caixa_tipos (longitud de campo) - value too long for type character varying(50) - - Ajuste en UAT conforme acordado, en espera de confirmación por parte de S3 para promoción a producción."</v>
+        <v>- mt_caixa_tipos (longitud de campo) value too long for type character varying(50) - Ajuste en UAT conforme acordado, en espera de confirmación por parte de S3 para promoción a producción.</v>
       </c>
       <c r="G10" t="str">
-        <v>31/10/2025_x000d_</v>
+        <v>31/10/2025</v>
       </c>
       <c r="H10" t="str">
         <v>Validación de lado S3_x000d_</v>
@@ -1381,25 +1381,25 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ajuste Proceso de Carga_x000d_</v>
+        <v>Ajuste Proceso de Carga</v>
       </c>
       <c r="B11" t="str">
-        <v>⚠️_x000d_</v>
+        <v>⚠️UAT</v>
       </c>
       <c r="C11" t="str">
-        <v>UAT</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="D11" t="str">
-        <v>NFQ / S3_x000d_</v>
+        <v>Ajuste de Interfaz Equity</v>
       </c>
       <c r="E11" t="str">
-        <v>Ajuste de Interfaz Equity_x000d_</v>
+        <v>- Fue incluido un nuevo campo, a espera de validación y promoción a PRD</v>
       </c>
       <c r="F11" t="str">
         <v>- Fue incluido un nuevo campo, a espera de validación y promoción a PRD_x000d_</v>
       </c>
       <c r="G11" t="str">
-        <v>21/01/2026_x000d_</v>
+        <v>21/01/2026</v>
       </c>
       <c r="H11" t="str">
         <v>Validación de lado S3_x000d_</v>
@@ -1407,25 +1407,25 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ajuste Proceso de Carga_x000d_</v>
+        <v>Ajuste Proceso de Carga</v>
       </c>
       <c r="B12" t="str">
-        <v>⚠️_x000d_</v>
+        <v>⚠️UAT</v>
       </c>
       <c r="C12" t="str">
-        <v>UAT</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="D12" t="str">
-        <v>NFQ / S3_x000d_</v>
+        <v>Ajuste de Carga ScriptByClient</v>
       </c>
       <c r="E12" t="str">
-        <v>Ajuste de Carga ScriptByClient_x000d_</v>
+        <v>- Fue realizado un ajuste en la carga de las tablas Megara que alimentan el mapeo SAC_BA_SCRIPT</v>
       </c>
       <c r="F12" t="str">
         <v>- Fue realizado un ajuste en la carga de las tablas Megara que alimentan el mapeo SAC_BA_SCRIPT_x000d_</v>
       </c>
       <c r="G12" t="str">
-        <v>28/01/2026_x000d_</v>
+        <v>28/01/2026</v>
       </c>
       <c r="H12" t="str">
         <v>Validación de lado S3_x000d_</v>
@@ -1433,80 +1433,80 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Información UAT_x000d_</v>
+        <v>Información UAT</v>
       </c>
       <c r="B13" t="str">
-        <v>⚫_x000d_</v>
+        <v>⚫UAT</v>
       </c>
       <c r="C13" t="str">
-        <v>UAT</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="D13" t="str">
-        <v>NFQ / S3_x000d_</v>
+        <v>Monitoreamento de cargas</v>
       </c>
       <c r="E13" t="str">
-        <v>Monitoreamento de cargas_x000d_</v>
+        <v>- Se requerirá de validaciones de informação por causa de los mapeos en UAT</v>
       </c>
       <c r="F13" t="str">
         <v>- Se requerirá de validaciones de información por causa de los mapeos en UAT_x000d_</v>
       </c>
       <c r="G13" t="str">
-        <v>31/10/2025_x000d_</v>
+        <v>31/10/2025</v>
       </c>
       <c r="H13" t="str">
-        <v>- S3 junto con NFQ revisará ambiente, a la espera de activación al equipo de proyecto_x000d_</v>
+        <v>- S3 junto con NFQ revisará ambiente, a la espera de activación al equipo de projeto_x000d_</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Datahub Api_x000d_</v>
+        <v>Datahub Api</v>
       </c>
       <c r="B14" t="str">
-        <v>▶️_x000d_</v>
+        <v>▶️UAT</v>
       </c>
       <c r="C14" t="str">
-        <v>UAT</v>
+        <v>NFQ / S3</v>
       </c>
       <c r="D14" t="str">
-        <v>NFQ / S3_x000d_</v>
+        <v>dh-motivobloqueio</v>
       </c>
       <c r="E14" t="str">
-        <v>dh-motivobloqueio_x000d_</v>
+        <v>- Api Motivo de Bloqueos han sido realizados los ajustes y está pendiente validación por parte de S3</v>
       </c>
       <c r="F14" t="str">
         <v>- Api Motivo de Bloqueos han sido realizados los ajustes y está pendiente validación por parte de S3</v>
       </c>
       <c r="G14" t="str">
-        <v>21/01/2026_x000d_</v>
+        <v>21/01/2026</v>
       </c>
       <c r="H14" t="str">
-        <v>- S3 notificará resultados de validaciones</v>
+        <v>- S3 notificará resultados de validaciones_x000d_</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Generacion informes_x000d_</v>
+        <v>Generacion informes</v>
       </c>
       <c r="B15" t="str">
-        <v>▶️_x000d_</v>
+        <v>▶️PRD</v>
       </c>
       <c r="C15" t="str">
-        <v>PRD</v>
+        <v>S3 / NFQ</v>
       </c>
       <c r="D15" t="str">
-        <v>S3 / NFQ_x000d_</v>
+        <v>Revisión de informes vacos</v>
       </c>
       <c r="E15" t="str">
-        <v>Revisión de informes vacos_x000d_</v>
+        <v>- Movimentaçao Swap, Dividendos juros apropiados, Posiçao Swap siendo generados en blanco. - Primeros dos arreglados, esperando detalles del tercero.</v>
       </c>
       <c r="F15" t="str">
-        <v>"- Movimentaçao Swap, Dividendos juros apropiados,Posiçao Swap.siendo generados en blanco. - - Primeros dos arreglados, esperando detalles del tercero.</v>
+        <v>- Movimentaçao Swap, Dividendos juros apropiados, Posiçao Swap siendo generados en blanco. - Primeros dos arreglados, esperando detalles del tercero.</v>
       </c>
       <c r="G15" t="str">
-        <v>29/01/2026_x000d_</v>
+        <v>29/01/2026</v>
       </c>
       <c r="H15" t="str">
-        <v>"- S3 validará arreglos en los informes. - - S3 compartirá detalles de PS para poder dar soporte."</v>
+        <v>- S3 validará arreglos en los informes. - S3 compartirá detalles de PS para poder dar suporte._x000d_</v>
       </c>
     </row>
     <row r="16">
@@ -1514,19 +1514,19 @@
         <v>Nota de Liquidaçao de Renda Fixa</v>
       </c>
       <c r="B16" t="str">
-        <v>▶️</v>
+        <v>▶️PRD</v>
       </c>
       <c r="C16" t="str">
-        <v>PRD</v>
+        <v>S3 / NFQ</v>
       </c>
       <c r="D16" t="str">
-        <v>S3 / NFQ</v>
+        <v>Generación de informe</v>
       </c>
       <c r="E16" t="str">
-        <v>Generación de informe</v>
+        <v>- S3 en análisis de cambio de plantilla para casos sin información. - S3 reporta error en generación de informe. - NFQ hizo ajustes.</v>
       </c>
       <c r="F16" t="str">
-        <v>"- S3 en análisis de cambio de plantilla para casos sin información. - - S3 reporta error en generación de informe. - - NFQ hizo ajustes."</v>
+        <v>- S3 en análisis de cambio de plantilla para casos sin información. - S3 reporta error en generación de informe. - NFQ hizo ajustes.</v>
       </c>
       <c r="G16" t="str">
         <v>09/02/2026</v>
@@ -1535,14 +1535,9 @@
         <v>- S3 analizará cambio de plantilla</v>
       </c>
     </row>
-    <row r="17">
-      <c r="E17" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -402,14 +402,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H12"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="50.00390625" customWidth="1"/>
-    <col min="6" max="6" width="50.00390625" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" customWidth="1"/>
-    <col min="8" max="8" width="42.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -505,7 +505,7 @@
         <v>16/06/2026</v>
       </c>
       <c r="H3" t="str">
-        <v>_x000d_</v>
+        <v>-</v>
       </c>
     </row>
     <row r="4">
@@ -531,7 +531,7 @@
         <v>17/06/2026</v>
       </c>
       <c r="H4" t="str">
-        <v>_x000d_</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5">
@@ -557,7 +557,7 @@
         <v>16/06/2026</v>
       </c>
       <c r="H5" t="str">
-        <v>_x000d_</v>
+        <v>-</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +583,7 @@
         <v>16/06/2026</v>
       </c>
       <c r="H6" t="str">
-        <v>_x000d_</v>
+        <v>-</v>
       </c>
     </row>
     <row r="7">
@@ -609,7 +609,7 @@
         <v>17/06/2026</v>
       </c>
       <c r="H7" t="str">
-        <v>_x000d_</v>
+        <v>-</v>
       </c>
     </row>
     <row r="8">
@@ -753,14 +753,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H7"/>
   <cols>
-    <col min="1" max="1" width="24.50390625" customWidth="1"/>
-    <col min="2" max="2" width="24.50390625" customWidth="1"/>
-    <col min="3" max="3" width="24.50390625" customWidth="1"/>
-    <col min="4" max="4" width="24.50390625" customWidth="1"/>
-    <col min="5" max="5" width="24.50390625" customWidth="1"/>
-    <col min="6" max="6" width="24.50390625" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" customWidth="1"/>
-    <col min="8" max="8" width="24.50390625" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -974,14 +974,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <cols>
-    <col min="1" max="1" width="24.50390625" customWidth="1"/>
-    <col min="2" max="2" width="24.50390625" customWidth="1"/>
-    <col min="3" max="3" width="24.50390625" customWidth="1"/>
-    <col min="4" max="4" width="24.50390625" customWidth="1"/>
-    <col min="5" max="5" width="24.50390625" customWidth="1"/>
-    <col min="6" max="6" width="24.50390625" customWidth="1"/>
-    <col min="7" max="7" width="24.50390625" customWidth="1"/>
-    <col min="8" max="8" width="24.50390625" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -1091,14 +1091,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H16"/>
   <cols>
-    <col min="1" max="1" width="50.00390625" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="39.00390625" customWidth="1"/>
-    <col min="5" max="5" width="50.00390625" customWidth="1"/>
-    <col min="6" max="6" width="50.00390625" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" customWidth="1"/>
-    <col min="8" max="8" width="50.00390625" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -402,14 +402,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H12"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -479,7 +479,7 @@
         <v>09/04/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>-----------------------_x000d_</v>
+        <v>-----------------------</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         <v>10/06/2026</v>
       </c>
       <c r="H8" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
+        <v>- S3 validará desarrollo</v>
       </c>
     </row>
     <row r="9">
@@ -661,7 +661,7 @@
         <v>15/06/2026</v>
       </c>
       <c r="H9" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
+        <v>- S3 validará desarrollo</v>
       </c>
     </row>
     <row r="10">
@@ -687,7 +687,7 @@
         <v>17/06/2026</v>
       </c>
       <c r="H10" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
+        <v>- S3 validará desarrollo</v>
       </c>
     </row>
     <row r="11">
@@ -713,7 +713,7 @@
         <v>27/05/2026</v>
       </c>
       <c r="H11" t="str">
-        <v>- NFQ ajustara segun el orden de prioridad de tarefas_x000d_</v>
+        <v>- NFQ ajustara segun el orden de prioridad de tarefas</v>
       </c>
     </row>
     <row r="12">
@@ -753,14 +753,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H7"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -809,155 +809,155 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Nuevos reportes</v>
+      </c>
+      <c r="B2" t="str">
         <v>Completado</v>
       </c>
-      <c r="B2" t="str">
-        <v>PRD</v>
-      </c>
       <c r="C2" t="str">
-        <v>NFQ / S3</v>
+        <v>PRD</v>
       </c>
       <c r="D2" t="str">
+        <v>NFQ / S3</v>
+      </c>
+      <c r="E2" t="str">
         <v>Creación de reporte: Relatório de Estoque de Cotas de Fundos</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>- Informe Disponibilizado en PRD</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>27/05/2026</v>
       </c>
-      <c r="G2" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
-      </c>
       <c r="H2" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
+        <v>- S3 validará desarrollo</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>Nuevos reportes</v>
+      </c>
+      <c r="B3" t="str">
         <v>Completado</v>
       </c>
-      <c r="B3" t="str">
-        <v>PRD</v>
-      </c>
       <c r="C3" t="str">
-        <v>NFQ / S3</v>
+        <v>PRD</v>
       </c>
       <c r="D3" t="str">
+        <v>NFQ / S3</v>
+      </c>
+      <c r="E3" t="str">
         <v>Creación de reporte: Relatório de Estoque de Futuros</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>- Informe Disponibilizado en PRD</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>27/05/2026</v>
       </c>
-      <c r="G3" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
-      </c>
       <c r="H3" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
+        <v>- S3 validará desarrollo</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>Nuevos reportes</v>
+      </c>
+      <c r="B4" t="str">
         <v>Completado</v>
       </c>
-      <c r="B4" t="str">
-        <v>PRD</v>
-      </c>
       <c r="C4" t="str">
-        <v>NFQ / S3</v>
+        <v>PRD</v>
       </c>
       <c r="D4" t="str">
+        <v>NFQ / S3</v>
+      </c>
+      <c r="E4" t="str">
         <v>Creación de reporte: Relatório de Estoque de RV</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>- Informe Disponibilizado en PRD</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>03/06/2026</v>
       </c>
-      <c r="G4" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
-      </c>
       <c r="H4" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
+        <v>- S3 validará desarrollo</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>Nuevos reportes</v>
+      </c>
+      <c r="B5" t="str">
         <v>Completado</v>
       </c>
-      <c r="B5" t="str">
-        <v>PRD</v>
-      </c>
       <c r="C5" t="str">
-        <v>NFQ / S3</v>
+        <v>PRD</v>
       </c>
       <c r="D5" t="str">
+        <v>NFQ / S3</v>
+      </c>
+      <c r="E5" t="str">
         <v>Creación de reporte: Relatório de Estoque de RF</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>- Informe Disponibilizado en PRD</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>27/05/2026</v>
       </c>
-      <c r="G5" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
-      </c>
       <c r="H5" t="str">
-        <v>- S3 validará desarrollo_x000d_</v>
+        <v>- S3 validará desarrollo</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>Demonstrativo de caixa</v>
+      </c>
+      <c r="B6" t="str">
         <v>Completado</v>
       </c>
-      <c r="B6" t="str">
-        <v>PRD</v>
-      </c>
       <c r="C6" t="str">
+        <v>PRD</v>
+      </c>
+      <c r="D6" t="str">
         <v>S3 / NFQ / VERMEG</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>Saldos</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>- Vermeg ha modificado la configuración de SupervisionDashboard en PRD para que se ejecute a las 06:00 (Horário de Brasilia)</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>18/05/2026</v>
       </c>
-      <c r="G6" t="str">
-        <v>NA_x000d_</v>
-      </c>
       <c r="H6" t="str">
-        <v>NA_x000d_</v>
+        <v>NA</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>Operações com Título de Renda Fixa</v>
+      </c>
+      <c r="B7" t="str">
         <v>En proceso</v>
       </c>
-      <c r="B7" t="str">
-        <v>PRD</v>
-      </c>
       <c r="C7" t="str">
+        <v>PRD</v>
+      </c>
+      <c r="D7" t="str">
         <v>S3 / NFQ / VERMEG</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>Reglas</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>- Se ha ajustado la regla de visualización de los saldos de los fondos MEGARA.</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>10/06/2026</v>
-      </c>
-      <c r="G7" t="str">
-        <v>- Se realizará desarrollo segun orden de priorización</v>
       </c>
       <c r="H7" t="str">
         <v>- Se realizará desarrollo segun orden de priorización</v>
@@ -974,14 +974,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -1051,7 +1051,7 @@
         <v>24/3/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>- Se seguirá compartiendo alerta_x000d_</v>
+        <v>- Se seguirá compartiendo alerta</v>
       </c>
     </row>
     <row r="3">
@@ -1091,14 +1091,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H16"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
@@ -1168,7 +1168,7 @@
         <v>03/04/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>Aguardando validacion de S3._x000d_</v>
+        <v>Aguardando validacion de S3.</v>
       </c>
     </row>
     <row r="3">
@@ -1194,7 +1194,7 @@
         <v>29/04/2026</v>
       </c>
       <c r="H3" t="str">
-        <v>-S3 compartirá template en csv. -NFQ ya ha vuelto a solicitar a S3 que envíe los arquivos_x000d_</v>
+        <v>-S3 compartirá template en csv. -NFQ ya ha vuelto a solicitar a S3 que envíe los arquivos</v>
       </c>
     </row>
     <row r="4">
@@ -1220,7 +1220,7 @@
         <v>22/04/2026</v>
       </c>
       <c r="H4" t="str">
-        <v>Espernado respuesta de Operaciones de Titulos ed Renda Variavel (cliente y fecha) S3 entregará informes de Extrato Simplifcado_x000d_</v>
+        <v>Espernado respuesta de Operaciones de Titulos ed Renda Variavel (cliente y fecha) S3 entregará informes de Extrato Simplifcado</v>
       </c>
     </row>
     <row r="5">
@@ -1246,7 +1246,7 @@
         <v>29/04/2026</v>
       </c>
       <c r="H5" t="str">
-        <v>- Validación de lado S3 para promocionar a UAT_x000d_</v>
+        <v>- Validación de lado S3 para promocionar a UAT</v>
       </c>
     </row>
     <row r="6">
@@ -1272,7 +1272,7 @@
         <v>07/07/2025</v>
       </c>
       <c r="H6" t="str">
-        <v>Validación de lado S3_x000d_</v>
+        <v>Validación de lado S3</v>
       </c>
     </row>
     <row r="7">
@@ -1298,7 +1298,7 @@
         <v>05/09/2025</v>
       </c>
       <c r="H7" t="str">
-        <v>Validación de lado S3_x000d_</v>
+        <v>Validación de lado S3</v>
       </c>
     </row>
     <row r="8">
@@ -1324,7 +1324,7 @@
         <v>28/10/2025</v>
       </c>
       <c r="H8" t="str">
-        <v>Validación de lado S3_x000d_</v>
+        <v>Validación de lado S3</v>
       </c>
     </row>
     <row r="9">
@@ -1350,7 +1350,7 @@
         <v>28/10/2025</v>
       </c>
       <c r="H9" t="str">
-        <v>Validación de lado S3_x000d_</v>
+        <v>Validación de lado S3</v>
       </c>
     </row>
     <row r="10">
@@ -1376,7 +1376,7 @@
         <v>31/10/2025</v>
       </c>
       <c r="H10" t="str">
-        <v>Validación de lado S3_x000d_</v>
+        <v>Validación de lado S3</v>
       </c>
     </row>
     <row r="11">
@@ -1402,7 +1402,7 @@
         <v>21/01/2026</v>
       </c>
       <c r="H11" t="str">
-        <v>Validación de lado S3_x000d_</v>
+        <v>Validación de lado S3</v>
       </c>
     </row>
     <row r="12">
@@ -1428,7 +1428,7 @@
         <v>28/01/2026</v>
       </c>
       <c r="H12" t="str">
-        <v>Validación de lado S3_x000d_</v>
+        <v>Validación de lado S3</v>
       </c>
     </row>
     <row r="13">
@@ -1454,7 +1454,7 @@
         <v>31/10/2025</v>
       </c>
       <c r="H13" t="str">
-        <v>- S3 junto con NFQ revisará ambiente, a la espera de activación al equipo de projeto_x000d_</v>
+        <v>- S3 junto con NFQ revisará ambiente, a la espera de activación al equipo de projeto.</v>
       </c>
     </row>
     <row r="14">
@@ -1480,7 +1480,7 @@
         <v>21/01/2026</v>
       </c>
       <c r="H14" t="str">
-        <v>- S3 notificará resultados de validaciones_x000d_</v>
+        <v>- S3 notificará resultados de validaciones_</v>
       </c>
     </row>
     <row r="15">
@@ -1506,7 +1506,7 @@
         <v>29/01/2026</v>
       </c>
       <c r="H15" t="str">
-        <v>- S3 validará arreglos en los informes. - S3 compartirá detalles de PS para poder dar suporte._x000d_</v>
+        <v>- S3 validará arreglos en los informes. - S3 compartirá detalles de PS para poder dar suporte.</v>
       </c>
     </row>
     <row r="16">

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -539,10 +539,10 @@
         <v>Ajuste Proceso de Carga</v>
       </c>
       <c r="B5" t="str">
-        <v>En proceso</v>
+        <v>Completado</v>
       </c>
       <c r="C5" t="str">
-        <v>UAT</v>
+        <v>PRD</v>
       </c>
       <c r="D5" t="str">
         <v>NFQ / S3</v>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BAU\status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0036AFD7-6145-4D2B-85EE-EFB1C633B923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C98F5E-87E8-49A0-91D1-3B38BADDFEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbMegara" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
     <sheet name="dbInfra" sheetId="3" r:id="rId3"/>
     <sheet name="dbUAT" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="173">
   <si>
     <t>tema</t>
   </si>
@@ -67,9 +80,6 @@
     <t>Creación de Solución</t>
   </si>
   <si>
-    <t>- Opciones de interfaces compartidas por S3: CGC Position, Valorized Position, Net Asset, Payable Receivable - La POC ha sido presentada.</t>
-  </si>
-  <si>
     <t>09/04/2026</t>
   </si>
   <si>
@@ -85,9 +95,6 @@
     <t>PRD</t>
   </si>
   <si>
-    <t>function_meg_cart_estat_gestor_t</t>
-  </si>
-  <si>
     <t>- Fue ajustada funcion de mapeamento</t>
   </si>
   <si>
@@ -97,165 +104,48 @@
     <t>-</t>
   </si>
   <si>
-    <t>function_meg_sac_cart_estat_administracao_t</t>
-  </si>
-  <si>
     <t>23/06/2026</t>
   </si>
   <si>
-    <t>function_meg_sac_cli_bas_compl_t</t>
-  </si>
-  <si>
     <t>22/06/2026</t>
   </si>
   <si>
-    <t>function_meg_sac_pl_cl_patrrv_t</t>
-  </si>
-  <si>
     <t>18/06/2026</t>
   </si>
   <si>
-    <t>function_meg_cart_pos_rv_t</t>
-  </si>
-  <si>
-    <t>function_meg_sac_stat_rv_cadpap_t</t>
-  </si>
-  <si>
-    <t>cs_detcash_flow_transf_pc</t>
-  </si>
-  <si>
-    <t>function_meg_cart_estat_clibas_t</t>
-  </si>
-  <si>
     <t>- Ajuste funcion de mapeamento</t>
   </si>
   <si>
     <t>- Espera de la solicitud de S3 para promocionar  a PRD</t>
   </si>
   <si>
-    <t>Activacion Function</t>
-  </si>
-  <si>
-    <t>Activación de la función function_meg_cart_estat_clibas_t en PRD</t>
-  </si>
-  <si>
     <t>Fue activada la function en PRD</t>
   </si>
   <si>
     <t>18/06/2027</t>
   </si>
   <si>
-    <t>Ajuste campo</t>
-  </si>
-  <si>
-    <t>No iniciado</t>
-  </si>
-  <si>
-    <t>Supervision Dashboard</t>
-  </si>
-  <si>
     <t>- S3 solicita ajuste de campo en supervision dhasboard</t>
   </si>
   <si>
     <t>27/05/2026</t>
   </si>
   <si>
-    <t>- NFQ ajustara segun el orden de prioridad de tarefas</t>
-  </si>
-  <si>
-    <t>Ajuste Option</t>
-  </si>
-  <si>
     <t>UAT</t>
   </si>
   <si>
-    <t>Options</t>
-  </si>
-  <si>
     <t>- Configuración de Rundeck para la interfaz de opciones</t>
   </si>
   <si>
     <t>17/06/2026</t>
   </si>
   <si>
-    <t>Agregar 2 columnas a la tabla de Contractual Client</t>
-  </si>
-  <si>
-    <t>Contractual Client</t>
-  </si>
-  <si>
-    <t>- Agregar 2 columnas a la tabla de Contractual Client</t>
-  </si>
-  <si>
     <t>09/06/2026</t>
   </si>
   <si>
-    <t>Nuevos reportes</t>
-  </si>
-  <si>
-    <t>Creación de reporte: Relatório de Estoque de Cotas de Fundos</t>
-  </si>
-  <si>
-    <t>- Informe Disponibilizado en PRD</t>
-  </si>
-  <si>
-    <t>- S3 validará desarrollo</t>
-  </si>
-  <si>
-    <t>Creación de reporte: Relatório de Estoque de Futuros</t>
-  </si>
-  <si>
-    <t>Creación de reporte: Relatório de Estoque de RV</t>
-  </si>
-  <si>
-    <t>03/06/2026</t>
-  </si>
-  <si>
-    <t>Creación de reporte: Relatório de Estoque de RF</t>
-  </si>
-  <si>
-    <t>Demonstrativo de caixa</t>
-  </si>
-  <si>
-    <t>S3 / NFQ / VERMEG</t>
-  </si>
-  <si>
-    <t>Saldos</t>
-  </si>
-  <si>
-    <t>- Vermeg ha modificado la configuración de SupervisionDashboard en PRD para que se ejecute a las 06:00 (Horário de Brasilia)</t>
-  </si>
-  <si>
-    <t>18/05/2026</t>
-  </si>
-  <si>
-    <t>Operações com Título de Renda Fixa</t>
-  </si>
-  <si>
-    <t>Reglas</t>
-  </si>
-  <si>
-    <t>- Se ha ajustado la regla de visualización de los saldos de los fondos MEGARA.</t>
-  </si>
-  <si>
-    <t>10/06/2026</t>
-  </si>
-  <si>
-    <t>- Se realizará desarrollo segun orden de priorización</t>
-  </si>
-  <si>
-    <t>Ajuste al informe del mapa de evolução de cotas.</t>
-  </si>
-  <si>
     <t>Relatório Mapa de evolução de Cotas - sem dados</t>
   </si>
   <si>
-    <t>- Cambio en la lógica del código del informe del mapa de evolução de cotas</t>
-  </si>
-  <si>
-    <t>- NFQ realizará una promoción para PRD</t>
-  </si>
-  <si>
     <t>Archivos Carga</t>
   </si>
   <si>
@@ -512,13 +402,166 @@
   </si>
   <si>
     <t>- S3 analizará cambio de plantilla</t>
+  </si>
+  <si>
+    <t>. Aguardando extracciones de interfaces especificas.</t>
+  </si>
+  <si>
+    <t>ENC: [JIRA] [JIRA] (SC-9009) Create field in FIDIC operation - RISK</t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_cart_pos_rf_t" que carrega a tabela SAC_RF_POS</t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_sac_pl_cl_patrrf_t" que carrega a tabela SAC_CL_PATRRF</t>
+  </si>
+  <si>
+    <t>ENC: [EXTERNAL] RES: [Aldrin] ContractualClien extraction - Fund Classification and Fund Sub Classification fields</t>
+  </si>
+  <si>
+    <t>[MEGARA X ALDRIN] Ajuste da função - trf_s3.function_meg_cart_caixa_mt_t</t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_cart_pos_rv_em_t" que carrega a tabela SAC_RV_EM_POS</t>
+  </si>
+  <si>
+    <t>[ALDRIN] SC-10115 : Valorized - Add two fields to be used for opening funds</t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_sac_pl_cl_patrfut_t_cgc" que carrega a tabela SAC_CL_PATRFUT</t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_cart_pos_fu_t_cgc" que carrega a tabela SAC_FU_POS</t>
+  </si>
+  <si>
+    <t>ENC: [EXTERNAL] RES: JIRA SC-9861: Campo código SubClasse não é preenchido no Megara</t>
+  </si>
+  <si>
+    <t>Correção na carga de campos na tabela “sss_est_com_mgc_t”</t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_cart_caixa_cpr_t10" que carrega a tabela SAC_CL_CPR (Corporate Actions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ALDRIN] Ajuste na função "function_meg_cart_estat_gestor_t" </t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_cart_estat_gestor_t" que carrega a tabela SAC_BA_ADMIN</t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_sac_cart_estat_administracao_t" que carrega a tabela SAC_BA_ADMINISTRACAO</t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_sac_cli_bas_compl_t" que carrega a tabela CLI_BAS_COMPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ALDRIN] Ajuste na função "function_meg_sac_pl_cl_patrrv_t" que carrega a tabela SAC_CL_PATRRV </t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_cart_pos_rv_t" que carrega a tabela RV_POS</t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_sac_stat_rv_cadpap_t" que carrega a tabela RV_CADPAP</t>
+  </si>
+  <si>
+    <t>Ativação da função function_meg_cart_estat_clibas_t em PRD</t>
+  </si>
+  <si>
+    <t>[MEGARA X ALDRIN] Alteração da função cs_detcash_flow_transf_pc</t>
+  </si>
+  <si>
+    <t>[ALDRIN] Ajuste na função "function_meg_cart_pos_rv_intermedia_t" que carrega a tabela RV_POS</t>
+  </si>
+  <si>
+    <t>Work in progress</t>
+  </si>
+  <si>
+    <t>Completada</t>
+  </si>
+  <si>
+    <t>Aguardando Respuesta</t>
+  </si>
+  <si>
+    <t>Assincronos</t>
+  </si>
+  <si>
+    <t>Esperando respuesta</t>
+  </si>
+  <si>
+    <t>PRD UAT</t>
+  </si>
+  <si>
+    <t>Creacion Assincronos</t>
+  </si>
+  <si>
+    <t>Espernado respuesta de Guilherme</t>
+  </si>
+  <si>
+    <t>Ajuste de Reglas</t>
+  </si>
+  <si>
+    <t>Fluxo de Caixa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajuste Informe </t>
+  </si>
+  <si>
+    <t>Ajuste Section Access</t>
+  </si>
+  <si>
+    <t>NFQ</t>
+  </si>
+  <si>
+    <t>Esperando respuesta para desarrollos</t>
+  </si>
+  <si>
+    <t>Ajustada relacion de seguridad para usauros</t>
+  </si>
+  <si>
+    <t>Informe Disponibilizado en PRD</t>
+  </si>
+  <si>
+    <t>14/97/2026</t>
+  </si>
+  <si>
+    <t>NFQ / S4</t>
+  </si>
+  <si>
+    <t>NFQ / S5</t>
+  </si>
+  <si>
+    <t>NFQ / S6</t>
+  </si>
+  <si>
+    <t>NFQ / S7</t>
+  </si>
+  <si>
+    <t>NFQ / S8</t>
+  </si>
+  <si>
+    <t>NFQ / S9</t>
+  </si>
+  <si>
+    <t>NFQ / S10</t>
+  </si>
+  <si>
+    <t>NFQ / S11</t>
+  </si>
+  <si>
+    <t>NFQ / S12</t>
+  </si>
+  <si>
+    <t>NFQ / S13</t>
+  </si>
+  <si>
+    <t>Aguardando Resuesta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -534,16 +577,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -551,13 +606,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -897,10 +968,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="104" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -932,7 +1008,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -949,14 +1025,14 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
       <c r="I2" t="s">
         <v>8</v>
       </c>
@@ -964,30 +1040,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
@@ -996,31 +1072,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
-        <v>24</v>
+      <c r="E4" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
       <c r="I4" t="s">
         <v>8</v>
       </c>
@@ -1028,31 +1104,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
-        <v>26</v>
+      <c r="E5" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
         <v>21</v>
       </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
       <c r="I5" t="s">
         <v>8</v>
       </c>
@@ -1060,31 +1136,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
-        <v>28</v>
+      <c r="E6" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
       <c r="I6" t="s">
         <v>8</v>
       </c>
@@ -1092,30 +1168,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
-        <v>30</v>
+      <c r="E7" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="I7" t="s">
         <v>8</v>
@@ -1124,30 +1200,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" t="s">
         <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
-        <v>31</v>
+      <c r="E8" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="I8" t="s">
         <v>8</v>
@@ -1156,30 +1232,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" t="s">
-        <v>32</v>
+      <c r="E9" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="I9" t="s">
         <v>8</v>
@@ -1188,30 +1264,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
-      <c r="E10" t="s">
-        <v>33</v>
+      <c r="E10" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I10" t="s">
         <v>8</v>
@@ -1220,30 +1296,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" t="s">
         <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
-      <c r="E11" t="s">
-        <v>37</v>
+      <c r="E11" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s">
         <v>8</v>
@@ -1252,30 +1328,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
-      <c r="E12" t="s">
-        <v>42</v>
+      <c r="E12" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G12" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="I12" t="s">
         <v>8</v>
@@ -1284,30 +1360,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="E13" t="s">
-        <v>48</v>
+      <c r="E13" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="I13" t="s">
         <v>8</v>
@@ -1316,30 +1392,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="E14" t="s">
-        <v>52</v>
+      <c r="E14" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I14" t="s">
         <v>8</v>
@@ -1348,20 +1424,201 @@
         <v>8</v>
       </c>
     </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17" t="s">
+        <v>164</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" t="s">
+        <v>169</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J14" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A3:A10 A2:E2 G2:J2 F4:J6 C3:D14 G14:J14 F13:G13 I13:J13 F12:G12 I12:J12 F10:J11 F7:G7 I7:J7 F8:G8 I8:J8 F9:G9 I9:J9 F3:G3 I3:J3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="41.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="106.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1387,192 +1644,91 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>160</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
       <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>60</v>
+        <v>157</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" t="s">
-        <v>61</v>
+        <v>159</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46200</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" t="s">
-        <v>76</v>
-      </c>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H8" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 D2 G2 B3:D3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1580,9 +1736,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1608,62 +1764,62 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="H2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 A3:H3 A2:F2 H2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1671,9 +1827,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1699,394 +1855,394 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="H4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="F5" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="G6" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="H6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="F10" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="F11" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="H11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="G12" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="H12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="G13" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="G15" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="H15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="F16" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="G16" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="H16" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C98F5E-87E8-49A0-91D1-3B38BADDFEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{3EBFCB60-C2C5-4C1D-9166-2DB65A7CEDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbMegara" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="dbUAT" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="157">
   <si>
     <t>tema</t>
   </si>
@@ -77,15 +100,9 @@
     <t>NFQ / S3</t>
   </si>
   <si>
-    <t>Creación de Solución</t>
-  </si>
-  <si>
     <t>09/04/2026</t>
   </si>
   <si>
-    <t>-----------------------</t>
-  </si>
-  <si>
     <t>Ajuste Proceso de Carga</t>
   </si>
   <si>
@@ -101,9 +118,6 @@
     <t>24/06/2026</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>23/06/2026</t>
   </si>
   <si>
@@ -116,18 +130,12 @@
     <t>- Ajuste funcion de mapeamento</t>
   </si>
   <si>
-    <t>- Espera de la solicitud de S3 para promocionar  a PRD</t>
-  </si>
-  <si>
     <t>Fue activada la function en PRD</t>
   </si>
   <si>
     <t>18/06/2027</t>
   </si>
   <si>
-    <t>- S3 solicita ajuste de campo en supervision dhasboard</t>
-  </si>
-  <si>
     <t>27/05/2026</t>
   </si>
   <si>
@@ -143,9 +151,6 @@
     <t>09/06/2026</t>
   </si>
   <si>
-    <t>Relatório Mapa de evolução de Cotas - sem dados</t>
-  </si>
-  <si>
     <t>Archivos Carga</t>
   </si>
   <si>
@@ -407,9 +412,6 @@
     <t>. Aguardando extracciones de interfaces especificas.</t>
   </si>
   <si>
-    <t>ENC: [JIRA] [JIRA] (SC-9009) Create field in FIDIC operation - RISK</t>
-  </si>
-  <si>
     <t>[ALDRIN] Ajuste na função "function_meg_cart_pos_rf_t" que carrega a tabela SAC_RF_POS</t>
   </si>
   <si>
@@ -419,15 +421,6 @@
     <t>ENC: [EXTERNAL] RES: [Aldrin] ContractualClien extraction - Fund Classification and Fund Sub Classification fields</t>
   </si>
   <si>
-    <t>[MEGARA X ALDRIN] Ajuste da função - trf_s3.function_meg_cart_caixa_mt_t</t>
-  </si>
-  <si>
-    <t>[ALDRIN] Ajuste na função "function_meg_cart_pos_rv_em_t" que carrega a tabela SAC_RV_EM_POS</t>
-  </si>
-  <si>
-    <t>[ALDRIN] SC-10115 : Valorized - Add two fields to be used for opening funds</t>
-  </si>
-  <si>
     <t>[ALDRIN] Ajuste na função "function_meg_sac_pl_cl_patrfut_t_cgc" que carrega a tabela SAC_CL_PATRFUT</t>
   </si>
   <si>
@@ -443,39 +436,12 @@
     <t>[ALDRIN] Ajuste na função "function_meg_cart_caixa_cpr_t10" que carrega a tabela SAC_CL_CPR (Corporate Actions)</t>
   </si>
   <si>
-    <t xml:space="preserve">[ALDRIN] Ajuste na função "function_meg_cart_estat_gestor_t" </t>
-  </si>
-  <si>
-    <t>[ALDRIN] Ajuste na função "function_meg_cart_estat_gestor_t" que carrega a tabela SAC_BA_ADMIN</t>
-  </si>
-  <si>
-    <t>[ALDRIN] Ajuste na função "function_meg_sac_cart_estat_administracao_t" que carrega a tabela SAC_BA_ADMINISTRACAO</t>
-  </si>
-  <si>
-    <t>[ALDRIN] Ajuste na função "function_meg_sac_cli_bas_compl_t" que carrega a tabela CLI_BAS_COMPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ALDRIN] Ajuste na função "function_meg_sac_pl_cl_patrrv_t" que carrega a tabela SAC_CL_PATRRV </t>
-  </si>
-  <si>
-    <t>[ALDRIN] Ajuste na função "function_meg_cart_pos_rv_t" que carrega a tabela RV_POS</t>
-  </si>
-  <si>
-    <t>[ALDRIN] Ajuste na função "function_meg_sac_stat_rv_cadpap_t" que carrega a tabela RV_CADPAP</t>
-  </si>
-  <si>
-    <t>Ativação da função function_meg_cart_estat_clibas_t em PRD</t>
-  </si>
-  <si>
     <t>[MEGARA X ALDRIN] Alteração da função cs_detcash_flow_transf_pc</t>
   </si>
   <si>
     <t>[ALDRIN] Ajuste na função "function_meg_cart_pos_rv_intermedia_t" que carrega a tabela RV_POS</t>
   </si>
   <si>
-    <t>Work in progress</t>
-  </si>
-  <si>
     <t>Completada</t>
   </si>
   <si>
@@ -494,83 +460,84 @@
     <t>Creacion Assincronos</t>
   </si>
   <si>
-    <t>Espernado respuesta de Guilherme</t>
-  </si>
-  <si>
-    <t>Ajuste de Reglas</t>
-  </si>
-  <si>
     <t>Fluxo de Caixa</t>
   </si>
   <si>
     <t xml:space="preserve">Ajuste Informe </t>
   </si>
   <si>
-    <t>Ajuste Section Access</t>
-  </si>
-  <si>
-    <t>NFQ</t>
-  </si>
-  <si>
-    <t>Esperando respuesta para desarrollos</t>
-  </si>
-  <si>
-    <t>Ajustada relacion de seguridad para usauros</t>
-  </si>
-  <si>
     <t>Informe Disponibilizado en PRD</t>
   </si>
   <si>
-    <t>14/97/2026</t>
-  </si>
-  <si>
-    <t>NFQ / S4</t>
-  </si>
-  <si>
-    <t>NFQ / S5</t>
-  </si>
-  <si>
-    <t>NFQ / S6</t>
-  </si>
-  <si>
-    <t>NFQ / S7</t>
-  </si>
-  <si>
-    <t>NFQ / S8</t>
-  </si>
-  <si>
-    <t>NFQ / S9</t>
-  </si>
-  <si>
-    <t>NFQ / S10</t>
-  </si>
-  <si>
-    <t>NFQ / S11</t>
-  </si>
-  <si>
-    <t>NFQ / S12</t>
-  </si>
-  <si>
-    <t>NFQ / S13</t>
-  </si>
-  <si>
-    <t>Aguardando Resuesta</t>
+    <t xml:space="preserve">A la espera de instrucciones por parte de Guilherme </t>
+  </si>
+  <si>
+    <t>Demontrativo de Caixa</t>
+  </si>
+  <si>
+    <t>Ajuste de logica en relacion a fecha de procesamiento del fondo</t>
+  </si>
+  <si>
+    <t>S3 compartira archivos necesarios</t>
+  </si>
+  <si>
+    <t>Fue identificado error por parte de vermeg</t>
+  </si>
+  <si>
+    <t>Aguardando Respuesta por parte de S3</t>
+  </si>
+  <si>
+    <t>Fue liberado en uat</t>
+  </si>
+  <si>
+    <t>Infores Estoque Fundos Private</t>
+  </si>
+  <si>
+    <t>En progreso</t>
+  </si>
+  <si>
+    <t>Validacion Informes</t>
+  </si>
+  <si>
+    <t>Bruna ha mandado una lamada para verificar informes, sin detalles compartidos</t>
+  </si>
+  <si>
+    <t>Se llevara a cabo reunin con Bruna y Jefferson</t>
+  </si>
+  <si>
+    <t>Esperando respuesta de Guilherme</t>
+  </si>
+  <si>
+    <t>Creacion de solucion</t>
+  </si>
+  <si>
+    <t>Option</t>
+  </si>
+  <si>
+    <t>Creacion de estrategia para tratamiento de Optios</t>
+  </si>
+  <si>
+    <t>Se esta desarrollando nueva estrategia para tratamiento de multiples archivos de Option en una sola distribucion con respecto a Opton</t>
+  </si>
+  <si>
+    <t>Ajuste Api</t>
+  </si>
+  <si>
+    <t>Ajuste de api papel</t>
+  </si>
+  <si>
+    <t>Se  modificara la logica de api para informaciones de orgen megara</t>
+  </si>
+  <si>
+    <t>El dia de hoy se liberara desarrollo en UAT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -598,7 +565,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -619,16 +586,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -968,12 +944,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="104" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1022,16 +999,16 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
@@ -1042,30 +1019,30 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
       <c r="H3" t="s">
-        <v>172</v>
-      </c>
-      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
         <v>8</v>
       </c>
       <c r="J3" t="s">
@@ -1074,28 +1051,28 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>124</v>
+      <c r="E4" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
@@ -1106,28 +1083,28 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="I5" t="s">
         <v>8</v>
@@ -1138,28 +1115,28 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="I6" t="s">
         <v>8</v>
@@ -1170,60 +1147,60 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>127</v>
+      <c r="E7" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
         <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>172</v>
+        <v>11</v>
       </c>
       <c r="I7" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>128</v>
+      <c r="E8" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I8" t="s">
         <v>8</v>
@@ -1234,28 +1211,28 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>129</v>
+      <c r="E9" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I9" t="s">
         <v>8</v>
@@ -1266,28 +1243,28 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>130</v>
+      <c r="E10" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I10" t="s">
         <v>8</v>
@@ -1298,307 +1275,81 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>131</v>
+      <c r="E11" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>132</v>
+      <c r="E12" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
         <v>29</v>
       </c>
-      <c r="G12" t="s">
-        <v>30</v>
-      </c>
       <c r="H12" t="s">
-        <v>172</v>
-      </c>
-      <c r="I12" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>133</v>
+      <c r="E13" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>33</v>
+        <v>155</v>
+      </c>
+      <c r="G13" s="3">
+        <v>46226</v>
       </c>
       <c r="H13" t="s">
-        <v>172</v>
-      </c>
-      <c r="I13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D15" t="s">
-        <v>162</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>146</v>
-      </c>
-      <c r="D17" t="s">
-        <v>164</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>146</v>
-      </c>
-      <c r="D18" t="s">
-        <v>165</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" t="s">
-        <v>167</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" t="s">
-        <v>168</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" t="s">
-        <v>169</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" t="s">
-        <v>146</v>
-      </c>
-      <c r="D23" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" t="s">
-        <v>146</v>
-      </c>
-      <c r="D24" t="s">
-        <v>171</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F24" t="s">
-        <v>19</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 A3:A10 A2:E2 G2:J2 F4:J6 C3:D14 G14:J14 F13:G13 I13:J13 F12:G12 I12:J12 F10:J11 F7:G7 I7:J7 F8:G8 I8:J8 F9:G9 I9:J9 F3:G3 I3:J3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A3:A5 A2:D2 G2 G5 C3:D5 G10 F9:G9 I9:J9 G8 I8:J8 F6:G6 F3:G3 I3:J3 F4:G4 I4:J4 I5:J5 F7:G7 I7:J7 I10:J10 I2:J2 A6 C6:D10 I6:J6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1609,7 +1360,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.125" bestFit="1" customWidth="1"/>
@@ -1646,84 +1397,110 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
         <v>148</v>
-      </c>
-      <c r="B2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="F3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
+        <v>135</v>
+      </c>
+      <c r="G3" s="3">
+        <v>46216</v>
       </c>
       <c r="H3" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>137</v>
       </c>
       <c r="F4" t="s">
-        <v>159</v>
-      </c>
-      <c r="G4" s="4">
-        <v>46200</v>
+        <v>138</v>
+      </c>
+      <c r="G4" s="3">
+        <v>46225</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" s="3">
+        <v>46226</v>
+      </c>
+      <c r="H5" t="s">
+        <v>147</v>
+      </c>
+    </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E14" s="2"/>
+      <c r="E14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1735,8 +1512,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="233.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1766,54 +1553,78 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" t="s">
-        <v>161</v>
+        <v>33</v>
+      </c>
+      <c r="G2" s="3">
+        <v>46217</v>
       </c>
       <c r="H2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" t="s">
-        <v>43</v>
-      </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G4" t="e" cm="1">
+        <f t="array" ref="G4">- Se probara en UAT el desarrollo</f>
+        <v>#NAME?</v>
       </c>
     </row>
   </sheetData>
@@ -1857,392 +1668,392 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>47</v>
       </c>
-      <c r="E3" t="s">
-        <v>53</v>
-      </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" t="s">
         <v>67</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
         <v>69</v>
       </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" t="s">
         <v>67</v>
-      </c>
-      <c r="B10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F12" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G13" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G15" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="H15" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
         <v>112</v>
       </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H16" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB378AF-4259-448D-BAFC-A6A3CF8D6A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD173CC0-B922-4770-A898-E3661A7B5D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbMegara" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="147">
   <si>
     <t>tema</t>
   </si>
@@ -467,13 +467,16 @@
     <t>Bug de Infra ocasiona fichero no existente en pasta innotech</t>
   </si>
   <si>
-    <t>30/0/2026</t>
-  </si>
-  <si>
     <t>Infraestructura</t>
   </si>
   <si>
     <t>S3 / NFQ /NTT</t>
+  </si>
+  <si>
+    <t>27/05/2027</t>
+  </si>
+  <si>
+    <t>27/05/2028</t>
   </si>
 </sst>
 </file>
@@ -543,12 +546,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1494,7 +1498,7 @@
       <c r="F2" t="s">
         <v>108</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H2" t="s">
@@ -1517,11 +1521,11 @@
       <c r="E3" t="s">
         <v>137</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="3">
-        <v>46216</v>
+      <c r="G3" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="H3" t="s">
         <v>139</v>
@@ -1546,8 +1550,8 @@
       <c r="F4" t="s">
         <v>110</v>
       </c>
-      <c r="G4" s="3">
-        <v>46225</v>
+      <c r="G4" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -1557,6 +1561,7 @@
       <c r="E13" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:H1 D2 G2 B3:D3" numberStoredAsText="1"/>
@@ -1659,7 +1664,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1668,7 +1673,7 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
         <v>115</v>
@@ -1677,7 +1682,7 @@
         <v>142</v>
       </c>
       <c r="G4" t="s">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD173CC0-B922-4770-A898-E3661A7B5D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E7E15B-93F7-4F29-BB68-8896A7F92830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbMegara" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="155">
   <si>
     <t>tema</t>
   </si>
@@ -89,30 +89,18 @@
     <t>27/05/2026</t>
   </si>
   <si>
-    <t>Archivos Carga</t>
-  </si>
-  <si>
     <t>S3 / VERMEG</t>
   </si>
   <si>
     <t>Modulos Megara</t>
   </si>
   <si>
-    <t>- Caida de MegaCustody Intraday</t>
-  </si>
-  <si>
     <t>24/3/2026</t>
   </si>
   <si>
     <t>- Se seguirá compartiendo alerta</t>
   </si>
   <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>Llamada de MEGARA desde Rundeck</t>
-  </si>
-  <si>
     <t>- S3 alineará internamente</t>
   </si>
   <si>
@@ -344,9 +332,6 @@
     <t>- S3 analizará cambio de plantilla</t>
   </si>
   <si>
-    <t>. Aguardando extracciones de interfaces especificas.</t>
-  </si>
-  <si>
     <t>Assincronos</t>
   </si>
   <si>
@@ -365,12 +350,6 @@
     <t xml:space="preserve">A la espera de instrucciones por parte de Guilherme </t>
   </si>
   <si>
-    <t>Demontrativo de Caixa</t>
-  </si>
-  <si>
-    <t>Ajuste de logica en relacion a fecha de procesamiento del fondo</t>
-  </si>
-  <si>
     <t>S3 compartira archivos necesarios</t>
   </si>
   <si>
@@ -383,12 +362,6 @@
     <t>Creacion de solucion</t>
   </si>
   <si>
-    <t>Creacion de estrategia para tratamiento de Optios</t>
-  </si>
-  <si>
-    <t>Ajuste na função "function_meg_cart_caixa_cpr_t3" que carrega a tabela SAC_CL_CPR (Lending / Borrowing Operations)</t>
-  </si>
-  <si>
     <t>Finalizada</t>
   </si>
   <si>
@@ -449,34 +422,85 @@
     <t>Finalizado</t>
   </si>
   <si>
-    <t>Relatorios de Estoques</t>
-  </si>
-  <si>
-    <t>Validados en UAT, se encontraron divergencias en PRD, en ajsute de logca</t>
-  </si>
-  <si>
     <t>En desarrollo</t>
   </si>
   <si>
     <t>Informes Estoque Fundos Private</t>
   </si>
   <si>
-    <t>Error en ClientInstruction al recibir xml con formato erroneo</t>
-  </si>
-  <si>
-    <t>Bug de Infra ocasiona fichero no existente en pasta innotech</t>
-  </si>
-  <si>
     <t>Infraestructura</t>
   </si>
   <si>
-    <t>S3 / NFQ /NTT</t>
-  </si>
-  <si>
     <t>27/05/2027</t>
   </si>
   <si>
     <t>27/05/2028</t>
+  </si>
+  <si>
+    <t>Conexión a la base de datos</t>
+  </si>
+  <si>
+    <t>Error en conexión a la base de datos Rundeck</t>
+  </si>
+  <si>
+    <t>S3 /NTT</t>
+  </si>
+  <si>
+    <t>SE / NTT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Error en formato xml / Registros Duplicados</t>
+  </si>
+  <si>
+    <t>ClientInstruction</t>
+  </si>
+  <si>
+    <t>Maquina Montada</t>
+  </si>
+  <si>
+    <t>Error en maquina montada de Rundeck</t>
+  </si>
+  <si>
+    <t>Todos los informes han sido entregados, a la espera de rspuesta</t>
+  </si>
+  <si>
+    <t>. Ayer recibimos extracciiones especificas</t>
+  </si>
+  <si>
+    <t>Option</t>
+  </si>
+  <si>
+    <t>En implementacion de Solucion</t>
+  </si>
+  <si>
+    <t>Despues de implementar S3 validara y se promocionara a PRD</t>
+  </si>
+  <si>
+    <t>Demontrativo de Caixa Robot</t>
+  </si>
+  <si>
+    <t>Relatorios de Estoque</t>
+  </si>
+  <si>
+    <t>Ajustando filtro por defecto</t>
+  </si>
+  <si>
+    <t>S3 validaá  y despues se llevara a PRD</t>
+  </si>
+  <si>
+    <t>Implementacion de tratamiento para cargas manuales</t>
+  </si>
+  <si>
+    <t>Rllagem Futuros</t>
+  </si>
+  <si>
+    <t>Ajuste de API</t>
+  </si>
+  <si>
+    <t>Se ha modificado un item referente a futuros</t>
+  </si>
+  <si>
+    <t>Esperando validacio prar promocionar a prd</t>
   </si>
 </sst>
 </file>
@@ -546,13 +570,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -938,7 +961,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -947,16 +970,16 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="G2" s="3">
         <v>46223.8125</v>
       </c>
       <c r="H2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
@@ -967,10 +990,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -979,16 +1002,16 @@
         <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="F3" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="G3" s="3">
         <v>46219.515972222223</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="I3" t="s">
         <v>8</v>
@@ -1002,7 +1025,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1010,14 +1033,14 @@
       <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>116</v>
+      <c r="E4" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="F4" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G4" s="3">
-        <v>46219.635416666664</v>
+        <v>46220.481249999997</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -1031,10 +1054,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -1043,22 +1066,16 @@
         <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="F5" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="G5" s="3">
         <v>46220.481249999997</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" t="s">
-        <v>8</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1066,7 +1083,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -1075,10 +1092,10 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="F6" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G6" s="3">
         <v>46220.489583333336</v>
@@ -1098,7 +1115,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1107,10 +1124,10 @@
         <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F7" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G7" s="3">
         <v>46220.502083333333</v>
@@ -1130,7 +1147,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -1139,10 +1156,10 @@
         <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F8" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G8" s="3">
         <v>46220.503472222219</v>
@@ -1162,7 +1179,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -1171,10 +1188,10 @@
         <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G9" s="3">
         <v>46220.714583333334</v>
@@ -1194,7 +1211,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -1203,10 +1220,10 @@
         <v>12</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F10" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G10" s="3">
         <v>46223.8125</v>
@@ -1226,7 +1243,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
@@ -1235,10 +1252,10 @@
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G11" s="3">
         <v>46226.669444444444</v>
@@ -1252,7 +1269,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
@@ -1261,10 +1278,10 @@
         <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G12" s="3">
         <v>46227.744444444441</v>
@@ -1278,7 +1295,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1287,10 +1304,10 @@
         <v>12</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="F13" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3">
         <v>46231.677777777775</v>
@@ -1304,19 +1321,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="F14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3">
         <v>46232.495138888888</v>
@@ -1330,19 +1347,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F15" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3">
         <v>46232.595833333333</v>
@@ -1356,19 +1373,19 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F16" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G16" s="3">
         <v>46226.675694444442</v>
@@ -1382,19 +1399,19 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F17" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3">
         <v>46232.532638888886</v>
@@ -1408,19 +1425,19 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" t="s">
         <v>127</v>
-      </c>
-      <c r="F18" t="s">
-        <v>136</v>
       </c>
       <c r="G18" s="3">
         <v>46232.532638888886</v>
@@ -1433,7 +1450,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 A3:A5 A2 C3:D3 I9:J9 I8:J8 I3:J3 I4:J4 I5:J5 I7:J7 I10:J10 I2:J2 A6 D6:D10 I6:J6 C2:D2 D4:D5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A2 C3:D3 I9:J9 I8:J8 I3:J3 I4:J4 I7:J7 I10:J10 I2:J2 A6 D6:D10 I6:J6 C2:D2 D4 A4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1481,33 +1498,33 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
         <v>106</v>
-      </c>
-      <c r="F2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -1519,21 +1536,21 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
+      </c>
+      <c r="F3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" t="s">
+        <v>131</v>
       </c>
       <c r="H3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1545,16 +1562,16 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
+      </c>
+      <c r="G4" t="s">
+        <v>132</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1612,7 +1629,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -1621,24 +1638,24 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1647,24 +1664,24 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="F3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
         <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1673,16 +1690,16 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -1691,7 +1708,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 A3 A2:F2 H2 G3:H3 C3:E3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 B2:E2 H2 G3:H3 C3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1732,7 +1749,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1741,24 +1758,24 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
         <v>27</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1767,24 +1784,24 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1793,24 +1810,24 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" t="s">
         <v>38</v>
-      </c>
-      <c r="E4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1822,146 +1839,146 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
         <v>47</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" t="s">
         <v>48</v>
       </c>
-      <c r="C6" t="s">
+      <c r="H6" t="s">
         <v>49</v>
-      </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" t="s">
         <v>54</v>
       </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="H7" t="s">
         <v>49</v>
-      </c>
-      <c r="D7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1969,25 +1986,25 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1995,129 +2012,129 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" t="s">
         <v>91</v>
       </c>
-      <c r="B15" t="s">
+      <c r="H15" t="s">
         <v>92</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" t="s">
-        <v>94</v>
-      </c>
-      <c r="G15" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" t="s">
         <v>97</v>
-      </c>
-      <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" t="s">
-        <v>99</v>
-      </c>
-      <c r="G16" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2366EB-6809-48F1-84D5-27D68D111E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64DEF5E-063E-421B-9EF9-6DBF1A8500C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbMegara" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="177">
   <si>
     <t>tema</t>
   </si>
@@ -93,15 +93,9 @@
     <t>S3 / VERMEG</t>
   </si>
   <si>
-    <t>Modulos Megara</t>
-  </si>
-  <si>
     <t>24/3/2026</t>
   </si>
   <si>
-    <t>- Se seguirá compartiendo alerta</t>
-  </si>
-  <si>
     <t>- S3 alineará internamente</t>
   </si>
   <si>
@@ -345,9 +339,6 @@
     <t>Creacion Assincronos</t>
   </si>
   <si>
-    <t xml:space="preserve">Ajuste Informe </t>
-  </si>
-  <si>
     <t xml:space="preserve">A la espera de instrucciones por parte de Guilherme </t>
   </si>
   <si>
@@ -360,21 +351,9 @@
     <t>function_meg_cart_pos_rv_em_t</t>
   </si>
   <si>
-    <t>En desarrollo</t>
-  </si>
-  <si>
-    <t>Informes Estoque Fundos Private</t>
-  </si>
-  <si>
-    <t>Infraestructura</t>
-  </si>
-  <si>
     <t>27/05/2027</t>
   </si>
   <si>
-    <t>27/05/2028</t>
-  </si>
-  <si>
     <t>Conexión a la base de datos</t>
   </si>
   <si>
@@ -384,24 +363,12 @@
     <t>S3 /NTT</t>
   </si>
   <si>
-    <t>SE / NTT</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Error en formato xml / Registros Duplicados</t>
   </si>
   <si>
     <t>ClientInstruction</t>
   </si>
   <si>
-    <t>Maquina Montada</t>
-  </si>
-  <si>
-    <t>Error en maquina montada de Rundeck</t>
-  </si>
-  <si>
-    <t>Todos los informes han sido entregados, a la espera de rspuesta</t>
-  </si>
-  <si>
     <t>Option</t>
   </si>
   <si>
@@ -411,36 +378,18 @@
     <t>Despues de implementar S3 validara y se promocionara a PRD</t>
   </si>
   <si>
-    <t>Demontrativo de Caixa Robot</t>
-  </si>
-  <si>
     <t>Relatorios de Estoque</t>
   </si>
   <si>
-    <t>Ajustando filtro por defecto</t>
-  </si>
-  <si>
-    <t>S3 validaá  y despues se llevara a PRD</t>
-  </si>
-  <si>
     <t>function_meg_cart_pos_fu_t</t>
   </si>
   <si>
-    <t>Query para Extração do Relatório Mapa de Evolução de Cotas do Portal</t>
-  </si>
-  <si>
-    <t>Work in progress</t>
-  </si>
-  <si>
     <t>Ajuste de función: "refresh_summary_netasset_calculations"</t>
   </si>
   <si>
     <t>Implementación: Tratamiento para cargas manuales</t>
   </si>
   <si>
-    <t>Resolución: PORTAL - Activos de futuros (SAC)</t>
-  </si>
-  <si>
     <t>En curso</t>
   </si>
   <si>
@@ -466,9 +415,6 @@
   </si>
   <si>
     <t>function_meg_cart_caixa_saldo_t</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t xml:space="preserve"> Tabla: RV_CADPAP</t>
@@ -521,7 +467,112 @@
     <t>Manejo de diferentes currency</t>
   </si>
   <si>
-    <t>Se incluiran nuevas monedas a ser mostradas en la extraccion del informe, actualmente en fase 1 (liitar a BRL)</t>
+    <t>Se incluiran nuevas monedas a ser mostradas en la extraccion del informe, actualmente en fase 1 (filtrar a BRL)</t>
+  </si>
+  <si>
+    <t>Fase 2 contempla el modo multicuenta</t>
+  </si>
+  <si>
+    <t>Filtro predeterminado para idioma</t>
+  </si>
+  <si>
+    <t>Desarrollo concluido en DEV.</t>
+  </si>
+  <si>
+    <t>Es necesario ayuda de s3 para  coordinar pruebas de aceptacion</t>
+  </si>
+  <si>
+    <t>Demonstraivo de Caixa</t>
+  </si>
+  <si>
+    <t>Optimizacion</t>
+  </si>
+  <si>
+    <t>Se efectuó optimización diminuyendo de los 20 min originales a 2:40</t>
+  </si>
+  <si>
+    <t>Es necesario coordinacion con s3 para pruebas de datos</t>
+  </si>
+  <si>
+    <t>Todos los informes han sido entregados y validados</t>
+  </si>
+  <si>
+    <t>Mapa de Evolucao de Cotas</t>
+  </si>
+  <si>
+    <t>Logica de construccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fue compartdo con S3 la logica de construccion del informe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA ? </t>
+  </si>
+  <si>
+    <t>Estoque Fundos Private</t>
+  </si>
+  <si>
+    <t>Operacoes com TRF</t>
+  </si>
+  <si>
+    <t>Verificacion de logica</t>
+  </si>
+  <si>
+    <t>Se ha compartido con S3 la lgica implementada para obtencion de valor "Valor Liquido"</t>
+  </si>
+  <si>
+    <t>A la espera de resppuesta de s3</t>
+  </si>
+  <si>
+    <t>Se analizara logica impleentada para integración SAC/Megara</t>
+  </si>
+  <si>
+    <t>NFQ compartirá logica realizada en el informe</t>
+  </si>
+  <si>
+    <t>PORTAL - Activos de futuros</t>
+  </si>
+  <si>
+    <t>Fueron realizados dos ustes en la logica de API:
+Cantidad de registros a ser mostrados
+Homologacion de formato SAC/Megara</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>N / A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Error en formato xml</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Se seguirá compartiendo alerta
+- Se modificara desarrollo interno para aceptaacion de la itnerfaz</t>
+  </si>
+  <si>
+    <t>Se modificara desarrollo interno para aceptaacion de la itnerfaz</t>
+  </si>
+  <si>
+    <t>CashTransferOrder</t>
+  </si>
+  <si>
+    <t>Megara</t>
+  </si>
+  <si>
+    <t>Error en interfaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3 / VERMEG </t>
+  </si>
+  <si>
+    <t>Modulos</t>
+  </si>
+  <si>
+    <t>Caida de modulos MEACUSTODY</t>
+  </si>
+  <si>
+    <t>S3 verificará con proovedor</t>
   </si>
 </sst>
 </file>
@@ -944,7 +995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="43.5" bestFit="1" customWidth="1"/>
@@ -990,7 +1041,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -999,16 +1050,16 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G2" s="2">
         <v>46223.8125</v>
       </c>
       <c r="H2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
@@ -1019,10 +1070,10 @@
     </row>
     <row r="3" spans="1:10" ht="110.25">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -1031,24 +1082,24 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G3" s="2">
         <v>46214</v>
       </c>
       <c r="H3" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1057,16 +1108,16 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="F4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="G4" s="2">
         <v>46219.515972222223</v>
       </c>
       <c r="H4" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
@@ -1075,9 +1126,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="204.75">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>14</v>
@@ -1089,19 +1140,16 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" t="s">
-        <v>136</v>
+        <v>163</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="G5" s="2">
-        <v>46220.481249999997</v>
+        <v>46245</v>
       </c>
       <c r="H5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" t="s">
-        <v>8</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
         <v>8</v>
@@ -1120,17 +1168,20 @@
       <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>131</v>
+      <c r="E6" t="s">
+        <v>126</v>
       </c>
       <c r="F6" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="G6" s="2">
-        <v>46239.602083333331</v>
+        <v>46220.481249999997</v>
       </c>
       <c r="H6" t="s">
-        <v>143</v>
+        <v>166</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
       </c>
       <c r="J6" t="s">
         <v>8</v>
@@ -1149,17 +1200,17 @@
       <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
-        <v>144</v>
+      <c r="E7" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="F7" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="G7" s="2">
-        <v>46239.863194444442</v>
+        <v>46239.602083333331</v>
       </c>
       <c r="H7" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="J7" t="s">
         <v>8</v>
@@ -1179,13 +1230,16 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>133</v>
+        <v>126</v>
+      </c>
+      <c r="F8" t="s">
+        <v>119</v>
       </c>
       <c r="G8" s="2">
-        <v>46239.879861111112</v>
+        <v>46239.863194444442</v>
       </c>
       <c r="H8" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="J8" t="s">
         <v>8</v>
@@ -1205,16 +1259,16 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F9" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="G9" s="2">
         <v>46240.621527777781</v>
       </c>
       <c r="H9" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1231,16 +1285,16 @@
         <v>12</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="F10" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G10" s="2">
         <v>46241.415277777778</v>
       </c>
       <c r="H10" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1257,16 +1311,16 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="G11" s="3">
         <v>46241.702777777777</v>
       </c>
       <c r="H11" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="I11" s="3"/>
     </row>
@@ -1284,16 +1338,16 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="F12" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G12" s="2">
         <v>46244.515277777777</v>
       </c>
       <c r="H12" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1310,16 +1364,16 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="F13" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G13" s="2">
         <v>46245.820138888892</v>
       </c>
       <c r="H13" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1336,16 +1390,16 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="F14" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="G14" s="2">
         <v>46245.840277777781</v>
       </c>
       <c r="H14" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1353,7 +1407,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -1362,13 +1416,16 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="F15" t="s">
+        <v>103</v>
       </c>
       <c r="G15" s="3">
-        <v>46246.818055555559</v>
+        <v>46246.723611111112</v>
       </c>
       <c r="H15" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1376,7 +1433,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -1385,16 +1442,16 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="F16" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="G16" s="3">
-        <v>46246.723611111112</v>
+        <v>46246.881944444445</v>
       </c>
       <c r="H16" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1402,7 +1459,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
@@ -1411,49 +1468,26 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="F17" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="G17" s="3">
-        <v>46246.881944444445</v>
+        <v>46246.907638888886</v>
       </c>
       <c r="H17" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
-        <v>150</v>
-      </c>
-      <c r="F18" t="s">
-        <v>142</v>
-      </c>
-      <c r="G18" s="3">
-        <v>46246.907638888886</v>
-      </c>
-      <c r="H18" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="E25" s="4"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="E27" s="4"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="E24" s="4"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="E26" s="4"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:8">
       <c r="E29" s="4"/>
@@ -1461,8 +1495,8 @@
     <row r="30" spans="1:8">
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:8">
-      <c r="E31" s="4"/>
+    <row r="32" spans="1:8">
+      <c r="E32" s="4"/>
     </row>
     <row r="33" spans="5:5">
       <c r="E33" s="4"/>
@@ -1479,8 +1513,8 @@
     <row r="37" spans="5:5">
       <c r="E37" s="4"/>
     </row>
-    <row r="38" spans="5:5">
-      <c r="E38" s="4"/>
+    <row r="39" spans="5:5">
+      <c r="E39" s="4"/>
     </row>
     <row r="40" spans="5:5">
       <c r="E40" s="4"/>
@@ -1491,20 +1525,17 @@
     <row r="42" spans="5:5">
       <c r="E42" s="4"/>
     </row>
-    <row r="43" spans="5:5">
-      <c r="E43" s="4"/>
-    </row>
-    <row r="45" spans="5:5">
-      <c r="E45" s="4"/>
-    </row>
-    <row r="47" spans="5:5">
-      <c r="E47" s="4"/>
+    <row r="44" spans="5:5">
+      <c r="E44" s="4"/>
+    </row>
+    <row r="46" spans="5:5">
+      <c r="E46" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E1 A2 C4:D4 J7 J6 I4:J4 I5:J5 J8 I2:J2 D6:D8 C2:D2 D5 A5 G1:J1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E1 A2 C4:D4 J8 J7 I4:J4 I6:J6 I2:J2 D7:D8 C2:D2 D6 A6 G1:J1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1520,7 +1551,7 @@
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="106.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="43.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1552,82 +1583,111 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="F2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="G2" s="2">
         <v>46246</v>
       </c>
+      <c r="H2" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
+        <v>145</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46244</v>
       </c>
       <c r="H3" t="s">
-        <v>104</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46246</v>
+      </c>
+      <c r="H4" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="F5" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1639,24 +1699,24 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="F6" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1665,18 +1725,69 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="F7" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="G7" s="3">
         <v>46246.818055555559</v>
       </c>
+      <c r="H7" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="B8" s="5"/>
-      <c r="G8" s="3"/>
+      <c r="A8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="3">
+        <v>46246</v>
+      </c>
+      <c r="H8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" s="3">
+        <v>46246</v>
+      </c>
+      <c r="H9" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="E15" s="1"/>
@@ -1686,14 +1797,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 D3 G3 B5:D5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 D5 G5 B6:D6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -1732,12 +1843,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="63">
       <c r="A2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" t="s">
         <v>117</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -1746,74 +1857,100 @@
         <v>17</v>
       </c>
       <c r="E2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
+      <c r="H2" s="6" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>134</v>
+        <v>170</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
+        <v>167</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46245</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
+        <v>48</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F4" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" t="s">
-        <v>11</v>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46245</v>
+      </c>
+      <c r="H5" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 B2:E2 H2 G3:H3 C3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 C2:D2 G4:H4 C4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1854,7 +1991,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1863,24 +2000,24 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1889,24 +2026,24 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1915,24 +2052,24 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>36</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1944,146 +2081,146 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
         <v>40</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
         <v>43</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>45</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
         <v>46</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" t="s">
         <v>47</v>
-      </c>
-      <c r="F6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
         <v>50</v>
       </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>51</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" t="s">
-        <v>54</v>
-      </c>
       <c r="H7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
         <v>55</v>
       </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>56</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>57</v>
       </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" t="s">
-        <v>59</v>
-      </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
         <v>60</v>
       </c>
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>61</v>
       </c>
-      <c r="D9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" t="s">
-        <v>63</v>
-      </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
         <v>64</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" t="s">
         <v>65</v>
       </c>
-      <c r="E10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" t="s">
-        <v>67</v>
-      </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2091,25 +2228,25 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
         <v>68</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>69</v>
       </c>
-      <c r="F11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" t="s">
-        <v>71</v>
-      </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2117,129 +2254,129 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
         <v>72</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>73</v>
       </c>
-      <c r="F12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" t="s">
-        <v>75</v>
-      </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" t="s">
+      <c r="E13" t="s">
         <v>77</v>
       </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>78</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" t="s">
         <v>79</v>
-      </c>
-      <c r="F13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
         <v>82</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E14" t="s">
         <v>83</v>
       </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" t="s">
         <v>84</v>
-      </c>
-      <c r="E14" t="s">
-        <v>85</v>
-      </c>
-      <c r="F14" t="s">
-        <v>85</v>
-      </c>
-      <c r="G14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
         <v>87</v>
       </c>
-      <c r="B15" t="s">
+      <c r="E15" t="s">
         <v>88</v>
       </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" t="s">
         <v>89</v>
       </c>
-      <c r="E15" t="s">
+      <c r="H15" t="s">
         <v>90</v>
-      </c>
-      <c r="F15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" t="s">
-        <v>91</v>
-      </c>
-      <c r="H15" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
         <v>93</v>
       </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" t="s">
         <v>94</v>
       </c>
-      <c r="E16" t="s">
+      <c r="H16" t="s">
         <v>95</v>
-      </c>
-      <c r="F16" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" t="s">
-        <v>96</v>
-      </c>
-      <c r="H16" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64DEF5E-063E-421B-9EF9-6DBF1A8500C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD4E929-30FB-40C6-877D-D63EF806ABA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbMegara" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="dbUAT" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="177">
   <si>
     <t>tema</t>
   </si>
@@ -90,9 +89,6 @@
     <t>27/05/2026</t>
   </si>
   <si>
-    <t>S3 / VERMEG</t>
-  </si>
-  <si>
     <t>24/3/2026</t>
   </si>
   <si>
@@ -348,9 +344,6 @@
     <t>Creacion de solucion</t>
   </si>
   <si>
-    <t>function_meg_cart_pos_rv_em_t</t>
-  </si>
-  <si>
     <t>27/05/2027</t>
   </si>
   <si>
@@ -363,79 +356,19 @@
     <t>S3 /NTT</t>
   </si>
   <si>
-    <t xml:space="preserve"> Error en formato xml / Registros Duplicados</t>
-  </si>
-  <si>
-    <t>ClientInstruction</t>
-  </si>
-  <si>
     <t>Option</t>
   </si>
   <si>
-    <t>En implementacion de Solucion</t>
-  </si>
-  <si>
-    <t>Despues de implementar S3 validara y se promocionara a PRD</t>
-  </si>
-  <si>
     <t>Relatorios de Estoque</t>
   </si>
   <si>
-    <t>function_meg_cart_pos_fu_t</t>
-  </si>
-  <si>
-    <t>Ajuste de función: "refresh_summary_netasset_calculations"</t>
-  </si>
-  <si>
     <t>Implementación: Tratamiento para cargas manuales</t>
   </si>
   <si>
     <t>En curso</t>
   </si>
   <si>
-    <t>Ajuste de función: "function_meg_sac_stat_fu_ativo_t"</t>
-  </si>
-  <si>
-    <t>function_meg_sac_stat_rv_cadpap_t1</t>
-  </si>
-  <si>
-    <t>refresh_summary_netasset_calculations</t>
-  </si>
-  <si>
     <t>function_meg_sac_stat_bas_cad_emp_t</t>
-  </si>
-  <si>
-    <t>function_meg_sac_stat_fu_ativo_t</t>
-  </si>
-  <si>
-    <t>function_meg_sac_pl_cl_patrfut_t</t>
-  </si>
-  <si>
-    <t>function_meg_cart_caixa_mt_t</t>
-  </si>
-  <si>
-    <t>function_meg_cart_caixa_saldo_t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tabla: RV_CADPAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tabla: BAS_CAD_EMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tabla: SAC_FU_POS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tabla: SAC_CL_PATRFUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tabla: SAC_RV_EM_POS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tabla: MT_CAIXA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tabla: CART_CAIXA_SALDO</t>
   </si>
   <si>
     <t>El conjunto de archivos compartido se encontraba incompleto, a la esperade nuevo paquete de interfaces
@@ -482,15 +415,9 @@
     <t>Es necesario ayuda de s3 para  coordinar pruebas de aceptacion</t>
   </si>
   <si>
-    <t>Demonstraivo de Caixa</t>
-  </si>
-  <si>
     <t>Optimizacion</t>
   </si>
   <si>
-    <t>Se efectuó optimización diminuyendo de los 20 min originales a 2:40</t>
-  </si>
-  <si>
     <t>Es necesario coordinacion con s3 para pruebas de datos</t>
   </si>
   <si>
@@ -506,9 +433,6 @@
     <t xml:space="preserve">Fue compartdo con S3 la logica de construccion del informe </t>
   </si>
   <si>
-    <t xml:space="preserve">NA ? </t>
-  </si>
-  <si>
     <t>Estoque Fundos Private</t>
   </si>
   <si>
@@ -518,16 +442,7 @@
     <t>Verificacion de logica</t>
   </si>
   <si>
-    <t>Se ha compartido con S3 la lgica implementada para obtencion de valor "Valor Liquido"</t>
-  </si>
-  <si>
     <t>A la espera de resppuesta de s3</t>
-  </si>
-  <si>
-    <t>Se analizara logica impleentada para integración SAC/Megara</t>
-  </si>
-  <si>
-    <t>NFQ compartirá logica realizada en el informe</t>
   </si>
   <si>
     <t>PORTAL - Activos de futuros</t>
@@ -544,25 +459,9 @@
     <t>N / A</t>
   </si>
   <si>
-    <t xml:space="preserve"> Error en formato xml</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Se seguirá compartiendo alerta
-- Se modificara desarrollo interno para aceptaacion de la itnerfaz</t>
-  </si>
-  <si>
-    <t>Se modificara desarrollo interno para aceptaacion de la itnerfaz</t>
-  </si>
-  <si>
-    <t>CashTransferOrder</t>
-  </si>
-  <si>
     <t>Megara</t>
   </si>
   <si>
-    <t>Error en interfaz</t>
-  </si>
-  <si>
     <t xml:space="preserve">S3 / VERMEG </t>
   </si>
   <si>
@@ -573,13 +472,113 @@
   </si>
   <si>
     <t>S3 verificará con proovedor</t>
+  </si>
+  <si>
+    <t>function_meg_cart_pos_fi_t_cc</t>
+  </si>
+  <si>
+    <t>Liberado en UAT</t>
+  </si>
+  <si>
+    <t>En monitoreamento para carga a PRD</t>
+  </si>
+  <si>
+    <t>Interfaces</t>
+  </si>
+  <si>
+    <t>Se ha compartido con S3 la lgica implementada para obtencion de valor "Valor Liquido" y Jur/prejuizo</t>
+  </si>
+  <si>
+    <t>Se efectuó optimización diminuyendo de los 20 min originales a 2:40 min</t>
+  </si>
+  <si>
+    <t>Nuevo Jira NTT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N / A </t>
+  </si>
+  <si>
+    <t>S3 /NFQ / NTT</t>
+  </si>
+  <si>
+    <t>Asigacion de usuario</t>
+  </si>
+  <si>
+    <t>NTT ha implementado nuevo flujo de soporte. A la espera de asigancion de usaurios para NFQ</t>
+  </si>
+  <si>
+    <t>20/08/206</t>
+  </si>
+  <si>
+    <t>NTT ompartirá usuario.
+Se alineara con s3 el nuevo flujo a ser realizado</t>
+  </si>
+  <si>
+    <t>Tabla: SAC_RV_EM_POS_REMUNERACAO (PK duplicada)</t>
+  </si>
+  <si>
+    <t>Tabla: SAC_FI_POS (para grabar totalizada la posicion para mas de una moneda)</t>
+  </si>
+  <si>
+    <t>function_meg_sac_pos_rv_em_rem_t</t>
+  </si>
+  <si>
+    <t>Tabla: BAS_CAD_EMP (Grabar el campo "cod_emp")</t>
+  </si>
+  <si>
+    <t>function_meg_sac_stat_rv_em_pos_ta_re_t</t>
+  </si>
+  <si>
+    <t>Tabla: SAC_RV_EM_POS_TAXA_REGISTRO (Pk duplicada)</t>
+  </si>
+  <si>
+    <t>"Error" en generación</t>
+  </si>
+  <si>
+    <t>NFQ fue notificado de un valor no esperado por S3, sin embargo, fue constatado que rflejaba correctamente a la informacion presente en la base de datos</t>
+  </si>
+  <si>
+    <t>Duplicados en mapeo de sac_stat_fu_cotativo_t (4000)</t>
+  </si>
+  <si>
+    <t>Es necesaria la validacion del codigo de mapeo</t>
+  </si>
+  <si>
+    <t>Duplicados</t>
+  </si>
+  <si>
+    <t>Mapementos</t>
+  </si>
+  <si>
+    <t>NFQ / S3 / VERMEG</t>
+  </si>
+  <si>
+    <t>Client Balance</t>
+  </si>
+  <si>
+    <t>XML con registros duplicados</t>
+  </si>
+  <si>
+    <t>S3 se encuentra en alaisis con VERMEG</t>
+  </si>
+  <si>
+    <t>Client Instruction</t>
+  </si>
+  <si>
+    <t>Valores de campos demsiado grandes impiden insercion en tablas de la ddbb</t>
+  </si>
+  <si>
+    <t>S3 en comunicación con el usaurio</t>
+  </si>
+  <si>
+    <t>Seurity Prices</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -603,6 +602,12 @@
       <color rgb="FFCE9178"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -644,7 +649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -656,6 +661,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -995,13 +1001,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="43.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="104" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="6" max="6" width="37.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1041,7 +1047,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -1050,16 +1056,16 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="G2" s="2">
         <v>46223.8125</v>
       </c>
       <c r="H2" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
@@ -1070,10 +1076,10 @@
     </row>
     <row r="3" spans="1:10" ht="110.25">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -1082,24 +1088,24 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="G3" s="2">
         <v>46214</v>
       </c>
       <c r="H3" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1108,16 +1114,16 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="G4" s="2">
-        <v>46219.515972222223</v>
+        <v>46254</v>
       </c>
       <c r="H4" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
@@ -1126,9 +1132,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="204.75">
+    <row r="5" spans="1:10" ht="63">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>14</v>
@@ -1140,114 +1146,102 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="G5" s="2">
         <v>46245</v>
       </c>
       <c r="H5" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="J5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" ht="31.5">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" t="s">
-        <v>119</v>
+        <v>176</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="G6" s="2">
-        <v>46220.481249999997</v>
+        <v>46259</v>
       </c>
       <c r="H6" t="s">
-        <v>166</v>
-      </c>
-      <c r="I6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="31.5">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" t="s">
-        <v>120</v>
+        <v>169</v>
+      </c>
+      <c r="E7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="G7" s="2">
-        <v>46239.602083333331</v>
+        <v>46258</v>
       </c>
       <c r="H7" t="s">
-        <v>166</v>
-      </c>
-      <c r="J7" t="s">
-        <v>8</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" t="s">
-        <v>119</v>
+        <v>170</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="G8" s="2">
-        <v>46239.863194444442</v>
+        <v>46260</v>
       </c>
       <c r="H8" t="s">
-        <v>166</v>
-      </c>
-      <c r="J8" t="s">
-        <v>8</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>14</v>
@@ -1259,21 +1253,21 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G9" s="2">
-        <v>46240.621527777781</v>
+        <v>158</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G9" s="3">
+        <v>46254</v>
       </c>
       <c r="H9" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>14</v>
@@ -1284,22 +1278,22 @@
       <c r="D10" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F10" t="s">
-        <v>122</v>
-      </c>
-      <c r="G10" s="2">
-        <v>46241.415277777778</v>
+      <c r="E10" t="s">
+        <v>157</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="3">
+        <v>46254</v>
       </c>
       <c r="H10" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>14</v>
@@ -1311,22 +1305,21 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" t="s">
-        <v>114</v>
+        <v>160</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="G11" s="3">
-        <v>46241.702777777777</v>
+        <v>46254</v>
       </c>
       <c r="H11" t="s">
-        <v>166</v>
-      </c>
-      <c r="I11" s="3"/>
+        <v>138</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>14</v>
@@ -1338,21 +1331,21 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>129</v>
-      </c>
-      <c r="F12" t="s">
-        <v>123</v>
-      </c>
-      <c r="G12" s="2">
-        <v>46244.515277777777</v>
+        <v>162</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G12" s="3">
+        <v>46255</v>
       </c>
       <c r="H12" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>14</v>
@@ -1364,178 +1357,74 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>129</v>
-      </c>
-      <c r="F13" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" s="2">
-        <v>46245.820138888892</v>
+        <v>167</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G13" s="3">
+        <v>46260</v>
       </c>
       <c r="H13" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>128</v>
-      </c>
-      <c r="F14" t="s">
-        <v>114</v>
-      </c>
-      <c r="G14" s="2">
-        <v>46245.840277777781</v>
-      </c>
-      <c r="H14" t="s">
-        <v>166</v>
-      </c>
-    </row>
     <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" t="s">
-        <v>130</v>
-      </c>
-      <c r="F15" t="s">
-        <v>103</v>
-      </c>
-      <c r="G15" s="3">
-        <v>46246.723611111112</v>
-      </c>
-      <c r="H15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" t="s">
-        <v>131</v>
-      </c>
-      <c r="F16" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16" s="3">
-        <v>46246.881944444445</v>
-      </c>
-      <c r="H16" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" t="s">
-        <v>132</v>
-      </c>
-      <c r="F17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G17" s="3">
-        <v>46246.907638888886</v>
-      </c>
-      <c r="H17" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="E15" s="4"/>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" s="4"/>
+    </row>
+    <row r="19" spans="5:5">
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="5:5">
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21" s="4"/>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="5:5">
       <c r="E24" s="4"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="25" spans="5:5">
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="5:5">
       <c r="E26" s="4"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="27" spans="5:5">
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="5:5">
       <c r="E28" s="4"/>
     </row>
-    <row r="29" spans="1:8">
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="5:5">
       <c r="E30" s="4"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="31" spans="5:5">
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="5:5">
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="5:5">
       <c r="E33" s="4"/>
     </row>
-    <row r="34" spans="5:5">
-      <c r="E34" s="4"/>
-    </row>
     <row r="35" spans="5:5">
       <c r="E35" s="4"/>
     </row>
-    <row r="36" spans="5:5">
-      <c r="E36" s="4"/>
-    </row>
     <row r="37" spans="5:5">
       <c r="E37" s="4"/>
-    </row>
-    <row r="39" spans="5:5">
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="5:5">
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="5:5">
-      <c r="E41" s="4"/>
-    </row>
-    <row r="42" spans="5:5">
-      <c r="E42" s="4"/>
-    </row>
-    <row r="44" spans="5:5">
-      <c r="E44" s="4"/>
-    </row>
-    <row r="46" spans="5:5">
-      <c r="E46" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E1 A2 C4:D4 J8 J7 I4:J4 I6:J6 I2:J2 D7:D8 C2:D2 D6 A6 G1:J1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E1 A2 C4:D4 I4:J4 I2:J2 C2:D2 G1:J1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1583,140 +1472,140 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G2" s="2">
         <v>46246</v>
       </c>
       <c r="H2" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="G3" s="2">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="H3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="F4" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="G4" s="2">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="H4" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
+        <v>149</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46246</v>
       </c>
       <c r="H5" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="G6" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>117</v>
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1725,68 +1614,68 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="F7" t="s">
-        <v>154</v>
-      </c>
-      <c r="G7" s="3">
-        <v>46246.818055555559</v>
+        <v>127</v>
+      </c>
+      <c r="G7" t="s">
+        <v>102</v>
       </c>
       <c r="H7" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="F8" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="G8" s="3">
-        <v>46246</v>
+        <v>46246.818055555559</v>
       </c>
       <c r="H8" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F9" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="G9" s="3">
         <v>46246</v>
       </c>
       <c r="H9" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1797,14 +1686,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 D5 G5 B6:D6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 D6 G6 B7:D7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -1843,114 +1732,88 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="63">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="B2" t="s">
-        <v>117</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>18</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="F3" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G3" s="2">
         <v>46245</v>
       </c>
       <c r="H3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="47.25">
       <c r="A4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>117</v>
+        <v>150</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="F4" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" t="s">
-        <v>174</v>
-      </c>
-      <c r="F5" t="s">
-        <v>175</v>
-      </c>
-      <c r="G5" s="2">
-        <v>46245</v>
-      </c>
-      <c r="H5" t="s">
-        <v>176</v>
+        <v>155</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 C2:D2 G4:H4 C4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 G2:H2 C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1991,7 +1854,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -2000,24 +1863,24 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -2026,24 +1889,24 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -2052,24 +1915,24 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
         <v>32</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>33</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>35</v>
-      </c>
-      <c r="H4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -2081,146 +1944,146 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
         <v>38</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
         <v>39</v>
-      </c>
-      <c r="G5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
         <v>41</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>43</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>44</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
         <v>45</v>
       </c>
-      <c r="F6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>46</v>
-      </c>
-      <c r="H6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
         <v>48</v>
       </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>49</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>50</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>51</v>
       </c>
-      <c r="G7" t="s">
-        <v>52</v>
-      </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
         <v>53</v>
       </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>55</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>56</v>
       </c>
-      <c r="G8" t="s">
-        <v>57</v>
-      </c>
       <c r="H8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
         <v>58</v>
       </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>59</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>60</v>
       </c>
-      <c r="E9" t="s">
-        <v>61</v>
-      </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
         <v>62</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>63</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
         <v>64</v>
       </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" t="s">
-        <v>65</v>
-      </c>
       <c r="H10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2228,25 +2091,25 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
         <v>66</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>67</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>68</v>
       </c>
-      <c r="G11" t="s">
-        <v>69</v>
-      </c>
       <c r="H11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2254,129 +2117,129 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" t="s">
         <v>70</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>71</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>72</v>
       </c>
-      <c r="G12" t="s">
-        <v>73</v>
-      </c>
       <c r="H12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
         <v>74</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
         <v>75</v>
       </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>76</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>77</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" t="s">
         <v>78</v>
-      </c>
-      <c r="G13" t="s">
-        <v>65</v>
-      </c>
-      <c r="H13" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
         <v>80</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
         <v>81</v>
       </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>82</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" t="s">
         <v>83</v>
-      </c>
-      <c r="F14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
         <v>85</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
         <v>86</v>
       </c>
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>87</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" t="s">
         <v>88</v>
       </c>
-      <c r="F15" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>89</v>
-      </c>
-      <c r="H15" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
         <v>91</v>
       </c>
-      <c r="B16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>92</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" t="s">
         <v>93</v>
       </c>
-      <c r="F16" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>94</v>
-      </c>
-      <c r="H16" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data_template.xlsx
+++ b/dashboard_data_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marco Pichardo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD4E929-30FB-40C6-877D-D63EF806ABA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F553438D-5C10-47FF-8F7C-60038FA66A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="151">
   <si>
     <t>tema</t>
   </si>
@@ -344,9 +344,6 @@
     <t>Creacion de solucion</t>
   </si>
   <si>
-    <t>27/05/2027</t>
-  </si>
-  <si>
     <t>Conexión a la base de datos</t>
   </si>
   <si>
@@ -359,38 +356,19 @@
     <t>Option</t>
   </si>
   <si>
-    <t>Relatorios de Estoque</t>
-  </si>
-  <si>
     <t>Implementación: Tratamiento para cargas manuales</t>
   </si>
   <si>
     <t>En curso</t>
-  </si>
-  <si>
-    <t>function_meg_sac_stat_bas_cad_emp_t</t>
   </si>
   <si>
     <t>El conjunto de archivos compartido se encontraba incompleto, a la esperade nuevo paquete de interfaces
 Pantalla gráfica V2 concluida.</t>
   </si>
   <si>
-    <t>Tiempos de carga</t>
-  </si>
-  <si>
-    <t>Ajustes para disminucion de tiempos</t>
-  </si>
-  <si>
     <t>S3 necesita compartir todos los conjuntos de archivos con informaciones.</t>
   </si>
   <si>
-    <t>Ajuste de mapeo cart_pos_rf_t</t>
-  </si>
-  <si>
-    <t>Se han realizado ajustes a proceso de carga NFQ.
-Ejecuciones  en  &lt; 5 min.</t>
-  </si>
-  <si>
     <t>Demonstrativo de Caixa</t>
   </si>
   <si>
@@ -409,33 +387,9 @@
     <t>Filtro predeterminado para idioma</t>
   </si>
   <si>
-    <t>Desarrollo concluido en DEV.</t>
-  </si>
-  <si>
     <t>Es necesario ayuda de s3 para  coordinar pruebas de aceptacion</t>
   </si>
   <si>
-    <t>Optimizacion</t>
-  </si>
-  <si>
-    <t>Es necesario coordinacion con s3 para pruebas de datos</t>
-  </si>
-  <si>
-    <t>Todos los informes han sido entregados y validados</t>
-  </si>
-  <si>
-    <t>Mapa de Evolucao de Cotas</t>
-  </si>
-  <si>
-    <t>Logica de construccion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fue compartdo con S3 la logica de construccion del informe </t>
-  </si>
-  <si>
-    <t>Estoque Fundos Private</t>
-  </si>
-  <si>
     <t>Operacoes com TRF</t>
   </si>
   <si>
@@ -445,20 +399,6 @@
     <t>A la espera de resppuesta de s3</t>
   </si>
   <si>
-    <t>PORTAL - Activos de futuros</t>
-  </si>
-  <si>
-    <t>Fueron realizados dos ustes en la logica de API:
-Cantidad de registros a ser mostrados
-Homologacion de formato SAC/Megara</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>N / A</t>
-  </si>
-  <si>
     <t>Megara</t>
   </si>
   <si>
@@ -474,9 +414,6 @@
     <t>S3 verificará con proovedor</t>
   </si>
   <si>
-    <t>function_meg_cart_pos_fi_t_cc</t>
-  </si>
-  <si>
     <t>Liberado en UAT</t>
   </si>
   <si>
@@ -489,55 +426,6 @@
     <t>Se ha compartido con S3 la lgica implementada para obtencion de valor "Valor Liquido" y Jur/prejuizo</t>
   </si>
   <si>
-    <t>Se efectuó optimización diminuyendo de los 20 min originales a 2:40 min</t>
-  </si>
-  <si>
-    <t>Nuevo Jira NTT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N / A </t>
-  </si>
-  <si>
-    <t>S3 /NFQ / NTT</t>
-  </si>
-  <si>
-    <t>Asigacion de usuario</t>
-  </si>
-  <si>
-    <t>NTT ha implementado nuevo flujo de soporte. A la espera de asigancion de usaurios para NFQ</t>
-  </si>
-  <si>
-    <t>20/08/206</t>
-  </si>
-  <si>
-    <t>NTT ompartirá usuario.
-Se alineara con s3 el nuevo flujo a ser realizado</t>
-  </si>
-  <si>
-    <t>Tabla: SAC_RV_EM_POS_REMUNERACAO (PK duplicada)</t>
-  </si>
-  <si>
-    <t>Tabla: SAC_FI_POS (para grabar totalizada la posicion para mas de una moneda)</t>
-  </si>
-  <si>
-    <t>function_meg_sac_pos_rv_em_rem_t</t>
-  </si>
-  <si>
-    <t>Tabla: BAS_CAD_EMP (Grabar el campo "cod_emp")</t>
-  </si>
-  <si>
-    <t>function_meg_sac_stat_rv_em_pos_ta_re_t</t>
-  </si>
-  <si>
-    <t>Tabla: SAC_RV_EM_POS_TAXA_REGISTRO (Pk duplicada)</t>
-  </si>
-  <si>
-    <t>"Error" en generación</t>
-  </si>
-  <si>
-    <t>NFQ fue notificado de un valor no esperado por S3, sin embargo, fue constatado que rflejaba correctamente a la informacion presente en la base de datos</t>
-  </si>
-  <si>
     <t>Duplicados en mapeo de sac_stat_fu_cotativo_t (4000)</t>
   </si>
   <si>
@@ -572,6 +460,37 @@
   </si>
   <si>
     <t>Seurity Prices</t>
+  </si>
+  <si>
+    <t>Desarrollo concluido en DEV.
+Desarrollo concluido en UAT</t>
+  </si>
+  <si>
+    <t>CashTransferORder</t>
+  </si>
+  <si>
+    <t>S3 validara ajuste</t>
+  </si>
+  <si>
+    <t>Asset</t>
+  </si>
+  <si>
+    <t>En desarrollo de nueva estructrua de xsd</t>
+  </si>
+  <si>
+    <t>Cambio de tipo de dato para todas las interfaces</t>
+  </si>
+  <si>
+    <t>NFQ terminará desarrollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En curso </t>
+  </si>
+  <si>
+    <t>NavBankBalance</t>
+  </si>
+  <si>
+    <t>En desarrollo de nueva interfaz</t>
   </si>
 </sst>
 </file>
@@ -610,21 +529,15 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -632,26 +545,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1001,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="43.5" bestFit="1" customWidth="1"/>
@@ -1042,12 +941,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="220.5">
+    <row r="2" spans="1:10" ht="63">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>109</v>
+      <c r="B2" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -1058,14 +957,14 @@
       <c r="E2" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="F2" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="1">
         <v>46223.8125</v>
       </c>
       <c r="H2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
@@ -1074,12 +973,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="110.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -1088,188 +987,185 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G3" s="2">
-        <v>46214</v>
+        <v>106</v>
+      </c>
+      <c r="F3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="1">
+        <v>46254</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>126</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="31.5">
       <c r="A4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>109</v>
+        <v>127</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" s="1">
+        <v>46259</v>
+      </c>
+      <c r="H4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="G4" s="2">
-        <v>46254</v>
-      </c>
-      <c r="H4" t="s">
-        <v>146</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="63">
-      <c r="A5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G5" s="2">
-        <v>46245</v>
+      <c r="G5" s="1">
+        <v>46273</v>
       </c>
       <c r="H5" t="s">
-        <v>138</v>
-      </c>
-      <c r="J5" t="s">
-        <v>8</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="31.5">
       <c r="A6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G6" s="1">
+        <v>46273</v>
+      </c>
+      <c r="H6" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" t="s">
-        <v>176</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G6" s="2">
-        <v>46259</v>
-      </c>
-      <c r="H6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="31.5">
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G7" s="1">
+        <v>46274</v>
+      </c>
+      <c r="H7" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G7" s="2">
-        <v>46258</v>
-      </c>
-      <c r="H7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+    </row>
+    <row r="8" spans="1:10" ht="31.5">
       <c r="A8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>109</v>
+        <v>127</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="G8" s="2">
-        <v>46260</v>
+        <v>137</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G8" s="1">
+        <v>46258</v>
       </c>
       <c r="H8" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>14</v>
+        <v>127</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G9" s="3">
-        <v>46254</v>
+        <v>134</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="1">
+        <v>46260</v>
       </c>
       <c r="H9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
@@ -1279,159 +1175,81 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G10" s="3">
-        <v>46254</v>
+        <v>131</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" s="2">
+        <v>46260</v>
       </c>
       <c r="H10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>160</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="G11" s="3">
-        <v>46254</v>
-      </c>
-      <c r="H11" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>162</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="G12" s="3">
-        <v>46255</v>
-      </c>
-      <c r="H12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
-        <v>167</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="G13" s="3">
-        <v>46260</v>
-      </c>
-      <c r="H13" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="E15" s="4"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="E14" s="3"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="4"/>
-    </row>
-    <row r="19" spans="5:5">
-      <c r="E19" s="4"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="3"/>
     </row>
     <row r="20" spans="5:5">
-      <c r="E20" s="4"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="5:5">
-      <c r="E21" s="4"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="5:5">
-      <c r="E23" s="4"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" spans="5:5">
-      <c r="E24" s="4"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="5:5">
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="5:5">
-      <c r="E26" s="4"/>
+      <c r="E25" s="3"/>
     </row>
     <row r="27" spans="5:5">
-      <c r="E27" s="4"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" spans="5:5">
-      <c r="E28" s="4"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="5:5">
+      <c r="E29" s="3"/>
     </row>
     <row r="30" spans="5:5">
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="5:5">
-      <c r="E31" s="4"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="32" spans="5:5">
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="5:5">
-      <c r="E33" s="4"/>
-    </row>
-    <row r="35" spans="5:5">
-      <c r="E35" s="4"/>
-    </row>
-    <row r="37" spans="5:5">
-      <c r="E37" s="4"/>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="34" spans="5:5">
+      <c r="E34" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E1 A2 C4:D4 I4:J4 I2:J2 C2:D2 G1:J1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E1 A2 C3:D3 I3:J3 I2:J2 C2:D2 G1:J1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="41.625" bestFit="1" customWidth="1"/>
@@ -1472,10 +1290,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
         <v>97</v>
@@ -1484,216 +1302,109 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="2">
+        <v>113</v>
+      </c>
+      <c r="G2" s="1">
         <v>46246</v>
       </c>
       <c r="H2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="31.5">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G3" s="2">
-        <v>46258</v>
+        <v>115</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="1">
+        <v>46244</v>
       </c>
       <c r="H3" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G4" s="2">
-        <v>46244</v>
+        <v>99</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>117</v>
       </c>
-      <c r="B5" t="s">
-        <v>109</v>
+      <c r="B5" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F5" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G5" s="2">
         <v>46246</v>
       </c>
       <c r="H5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G7" t="s">
-        <v>102</v>
-      </c>
-      <c r="H7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" t="s">
-        <v>130</v>
-      </c>
-      <c r="G8" s="3">
-        <v>46246.818055555559</v>
-      </c>
-      <c r="H8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G9" s="3">
-        <v>46246</v>
-      </c>
-      <c r="H9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="E15" s="1"/>
+        <v>119</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 D6 G6 B7:D7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 D4 G4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -1736,20 +1447,20 @@
       <c r="A2" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>109</v>
+      <c r="B2" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" t="s">
         <v>103</v>
-      </c>
-      <c r="F2" t="s">
-        <v>104</v>
       </c>
       <c r="G2" t="s">
         <v>17</v>
@@ -1760,54 +1471,28 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="F3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="2">
+        <v>123</v>
+      </c>
+      <c r="G3" s="1">
         <v>46245</v>
       </c>
       <c r="H3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="47.25">
-      <c r="A4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
